--- a/MDK-ARM/panzer_analysis.xlsx
+++ b/MDK-ARM/panzer_analysis.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="47">
   <si>
     <t>panzer</t>
   </si>
@@ -26,18 +26,18 @@
     <t>usart.o</t>
   </si>
   <si>
+    <t>tim.o</t>
+  </si>
+  <si>
     <t>encode.o</t>
   </si>
   <si>
-    <t>tim.o</t>
+    <t>interurp.o</t>
   </si>
   <si>
     <t>control_car.o</t>
   </si>
   <si>
-    <t>interurp.o</t>
-  </si>
-  <si>
     <t>emm_v5.o</t>
   </si>
   <si>
@@ -71,13 +71,10 @@
     <t>stm32f4xx_hal_cortex.o</t>
   </si>
   <si>
-    <t>pid.o</t>
+    <t>main.o</t>
   </si>
   <si>
     <t>stm32f4xx_hal_tim_ex.o</t>
-  </si>
-  <si>
-    <t>main.o</t>
   </si>
   <si>
     <t>mc_w.l</t>
@@ -248,9 +245,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>ram_percent!$A$3:$A$40</c:f>
+              <c:f>ram_percent!$A$3:$A$39</c:f>
               <c:strCache>
-                <c:ptCount val="38"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>startup_stm32f405xx.o</c:v>
                 </c:pt>
@@ -258,16 +255,16 @@
                   <c:v>usart.o</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>tim.o</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>encode.o</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>tim.o</c:v>
-                </c:pt>
                 <c:pt idx="4">
+                  <c:v>interurp.o</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>control_car.o</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>interurp.o</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>emm_v5.o</c:v>
@@ -281,7 +278,7 @@
                 <c:pt idx="9">
                   <c:v>system_stm32f4xx.o</c:v>
                 </c:pt>
-                <c:pt idx="37">
+                <c:pt idx="36">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -289,41 +286,41 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>ram_percent!$B$3:$B$40</c:f>
+              <c:f>ram_percent!$B$3:$B$39</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="38"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>32.52859115600586</c:v>
+                  <c:v>37.67476272583008</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>27.44599723815918</c:v>
+                  <c:v>31.7880802154541</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>19.56797981262207</c:v>
+                  <c:v>13.24503326416016</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>11.43583202362061</c:v>
+                  <c:v>7.947020053863525</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.907242774963379</c:v>
+                  <c:v>4.267844200134277</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.811944007873535</c:v>
+                  <c:v>3.568800687789917</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.6353240013122559</c:v>
+                  <c:v>0.7358351945877075</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.2858957946300507</c:v>
+                  <c:v>0.3311258256435394</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.2541296184062958</c:v>
+                  <c:v>0.2943340837955475</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.1270648092031479</c:v>
-                </c:pt>
-                <c:pt idx="37">
+                  <c:v>0.1471670418977737</c:v>
+                </c:pt>
+                <c:pt idx="36">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -391,121 +388,118 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>flash_percent!$A$3:$A$40</c:f>
+              <c:f>flash_percent!$A$3:$A$39</c:f>
               <c:strCache>
-                <c:ptCount val="38"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>stm32f4xx_hal_tim.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>stm32f4xx_hal_uart.o</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>stm32f4xx_hal_rcc.o</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>stm32f4xx_hal_dma.o</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>usart.o</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>tim.o</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>stm32f4xx_hal_gpio.o</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>interurp.o</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>stm32f4xx_it.o</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>mf_w.l</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>stm32f4xx_hal_cortex.o</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>startup_stm32f405xx.o</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>main.o</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>encode.o</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>stm32f4xx_hal_tim_ex.o</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>mc_w.l</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>stm32f4xx_hal.o</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>dmul.o</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>gpio.o</c:v>
+                </c:pt>
+                <c:pt idx="19">
                   <c:v>control_car.o</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>stm32f4xx_hal_uart.o</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>stm32f4xx_hal_rcc.o</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>stm32f4xx_hal_dma.o</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>interurp.o</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>usart.o</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>tim.o</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>encode.o</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>stm32f4xx_hal_gpio.o</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>stm32f4xx_it.o</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>mf_w.l</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>stm32f4xx_hal_cortex.o</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>pid.o</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>startup_stm32f405xx.o</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>stm32f4xx_hal_tim_ex.o</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>main.o</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>mc_w.l</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>stm32f4xx_hal.o</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>dmul.o</c:v>
-                </c:pt>
                 <c:pt idx="20">
-                  <c:v>gpio.o</c:v>
+                  <c:v>depilogue.o</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>depilogue.o</c:v>
+                  <c:v>dma.o</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>dma.o</c:v>
+                  <c:v>emm_v5.o</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>emm_v5.o</c:v>
+                  <c:v>uldiv.o</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>uldiv.o</c:v>
+                  <c:v>stm32f4xx_hal_msp.o</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>stm32f4xx_hal_msp.o</c:v>
+                  <c:v>dfixui.o</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>dfixui.o</c:v>
+                  <c:v>init.o</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>init.o</c:v>
+                  <c:v>system_stm32f4xx.o</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>system_stm32f4xx.o</c:v>
+                  <c:v>f2d.o</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>f2d.o</c:v>
+                  <c:v>memseta.o</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>memseta.o</c:v>
+                  <c:v>llushr.o</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>llushr.o</c:v>
+                  <c:v>llshl.o</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>llshl.o</c:v>
+                  <c:v>handlers.o</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>handlers.o</c:v>
+                  <c:v>entry9a.o</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>entry9a.o</c:v>
+                  <c:v>entry2.o</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>entry2.o</c:v>
+                  <c:v>entry5.o</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>entry5.o</c:v>
-                </c:pt>
-                <c:pt idx="37">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -513,122 +507,119 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>flash_percent!$B$3:$B$40</c:f>
+              <c:f>flash_percent!$B$3:$B$39</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="38"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>15.78655624389648</c:v>
+                  <c:v>19.66335868835449</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>14.07830905914307</c:v>
+                  <c:v>16.51273155212402</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>13.25710296630859</c:v>
+                  <c:v>11.41993999481201</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>9.168398857116699</c:v>
+                  <c:v>8.959861755371094</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7.193346977233887</c:v>
+                  <c:v>5.912818431854248</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.599445819854736</c:v>
+                  <c:v>5.783340454101563</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.747054576873779</c:v>
+                  <c:v>4.298662185668945</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4.643104553222656</c:v>
+                  <c:v>3.987915515899658</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.568953514099121</c:v>
+                  <c:v>3.685800552368164</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.451143503189087</c:v>
+                  <c:v>2.166594743728638</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.959112882614136</c:v>
+                  <c:v>2.080276250839233</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.739431738853455</c:v>
+                  <c:v>1.847216248512268</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.670131683349609</c:v>
+                  <c:v>1.38972806930542</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.524601578712463</c:v>
+                  <c:v>1.38972806930542</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.48302149772644</c:v>
+                  <c:v>1.320673227310181</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.060291051864624</c:v>
+                  <c:v>1.268882155418396</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.053361058235169</c:v>
+                  <c:v>1.186879634857178</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.018710970878601</c:v>
+                  <c:v>0.984031081199646</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.9528759717941284</c:v>
+                  <c:v>0.8545532822608948</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.790020763874054</c:v>
+                  <c:v>0.841605544090271</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.6860706806182861</c:v>
+                  <c:v>0.8027622103691101</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.644490659236908</c:v>
+                  <c:v>0.8027622103691101</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.644490659236908</c:v>
+                  <c:v>0.6732844114303589</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.5405405163764954</c:v>
+                  <c:v>0.4229607284069061</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.3395703434944153</c:v>
+                  <c:v>0.3193784952163696</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.2564102709293366</c:v>
+                  <c:v>0.2157962918281555</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.1732501685619354</c:v>
+                  <c:v>0.2071644365787506</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.1663201600313187</c:v>
+                  <c:v>0.1985325813293457</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.1593901664018631</c:v>
+                  <c:v>0.1640051752328873</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.1316701322793961</c:v>
+                  <c:v>0.1553733348846436</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.1247401237487793</c:v>
+                  <c:v>0.1381096243858337</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.1108801141381264</c:v>
+                  <c:v>0.1294777691364288</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.1039501056075096</c:v>
+                  <c:v>0.1294777691364288</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.1039501056075096</c:v>
+                  <c:v>0.03452740609645844</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.02772002853453159</c:v>
+                  <c:v>0.03452740609645844</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.02772002853453159</c:v>
+                  <c:v>0.01726370304822922</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.0138600142672658</c:v>
-                </c:pt>
-                <c:pt idx="37">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -733,8 +724,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H40" totalsRowCount="1">
-  <autoFilter ref="A2:H39"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H39" totalsRowCount="1">
+  <autoFilter ref="A2:H38"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="ram_percent" totalsRowFunction="sum"/>
@@ -750,8 +741,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H40" totalsRowCount="1">
-  <autoFilter ref="A2:H39"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H39" totalsRowCount="1">
+  <autoFilter ref="A2:H38"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="flash_percent" totalsRowFunction="sum"/>
@@ -1051,7 +1042,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -1064,28 +1055,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" t="s">
         <v>40</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>41</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>42</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>43</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>44</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>45</v>
-      </c>
-      <c r="H2" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1093,7 +1084,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>32.52859115600586</v>
+        <v>37.67476272583008</v>
       </c>
       <c r="C3" s="1">
         <v>1024</v>
@@ -1119,7 +1110,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>27.44599723815918</v>
+        <v>31.7880802154541</v>
       </c>
       <c r="C4" s="1">
         <v>864</v>
@@ -1145,25 +1136,25 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>19.56797981262207</v>
+        <v>13.24503326416016</v>
       </c>
       <c r="C5" s="1">
-        <v>616</v>
+        <v>360</v>
       </c>
       <c r="D5" s="1">
-        <v>1030</v>
+        <v>1340</v>
       </c>
       <c r="E5" s="1">
-        <v>814</v>
+        <v>1340</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>216</v>
+        <v>0</v>
       </c>
       <c r="H5" s="1">
-        <v>400</v>
+        <v>360</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1171,25 +1162,25 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>11.43583202362061</v>
+        <v>7.947020053863525</v>
       </c>
       <c r="C6" s="1">
-        <v>360</v>
+        <v>216</v>
       </c>
       <c r="D6" s="1">
-        <v>1340</v>
+        <v>322</v>
       </c>
       <c r="E6" s="1">
-        <v>1340</v>
+        <v>106</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="H6" s="1">
-        <v>360</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1197,25 +1188,25 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>3.907242774963379</v>
+        <v>4.267844200134277</v>
       </c>
       <c r="C7" s="1">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="D7" s="1">
-        <v>4063</v>
+        <v>924</v>
       </c>
       <c r="E7" s="1">
-        <v>4058</v>
+        <v>924</v>
       </c>
       <c r="F7" s="1">
         <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H7" s="1">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1223,25 +1214,25 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>3.811944007873535</v>
+        <v>3.568800687789917</v>
       </c>
       <c r="C8" s="1">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="D8" s="1">
-        <v>1616</v>
+        <v>195</v>
       </c>
       <c r="E8" s="1">
-        <v>1616</v>
+        <v>194</v>
       </c>
       <c r="F8" s="1">
         <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="1">
-        <v>120</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1249,7 +1240,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>0.6353240013122559</v>
+        <v>0.7358351945877075</v>
       </c>
       <c r="C9" s="1">
         <v>20</v>
@@ -1275,7 +1266,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>0.2858957946300507</v>
+        <v>0.3311258256435394</v>
       </c>
       <c r="C10" s="1">
         <v>9</v>
@@ -1301,7 +1292,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>0.2541296184062958</v>
+        <v>0.2943340837955475</v>
       </c>
       <c r="C11" s="1">
         <v>8</v>
@@ -1327,7 +1318,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.1270648092031479</v>
+        <v>0.1471670418977737</v>
       </c>
       <c r="C12" s="1">
         <v>4</v>
@@ -1348,35 +1339,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:8">
-      <c r="A40" t="s">
-        <v>39</v>
-      </c>
-      <c r="B40">
+    <row r="39" spans="1:8">
+      <c r="A39" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39">
         <f>SUBTOTAL(109,[ram_percent])</f>
         <v>0</v>
       </c>
-      <c r="C40">
+      <c r="C39">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="D40">
+      <c r="D39">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="E40">
+      <c r="E39">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F40">
+      <c r="F39">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G40">
+      <c r="G39">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H40">
+      <c r="H39">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>
@@ -1392,7 +1383,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -1405,28 +1396,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E2" t="s">
         <v>42</v>
       </c>
-      <c r="D2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>43</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>44</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>45</v>
-      </c>
-      <c r="H2" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1434,7 +1425,7 @@
         <v>11</v>
       </c>
       <c r="B3" s="2">
-        <v>15.78655624389648</v>
+        <v>19.66335868835449</v>
       </c>
       <c r="C3" s="1">
         <v>4556</v>
@@ -1457,45 +1448,45 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B4" s="2">
-        <v>14.07830905914307</v>
+        <v>16.51273155212402</v>
       </c>
       <c r="C4" s="1">
-        <v>4063</v>
+        <v>3826</v>
       </c>
       <c r="D4" s="1">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="E4" s="1">
-        <v>4058</v>
+        <v>3826</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H4" s="1">
-        <v>118</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="2">
-        <v>13.25710296630859</v>
+        <v>11.41993999481201</v>
       </c>
       <c r="C5" s="1">
-        <v>3826</v>
+        <v>2646</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
       </c>
       <c r="E5" s="1">
-        <v>3826</v>
+        <v>2646</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
@@ -1509,22 +1500,22 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" s="2">
-        <v>9.168398857116699</v>
+        <v>8.959861755371094</v>
       </c>
       <c r="C6" s="1">
-        <v>2646</v>
+        <v>2076</v>
       </c>
       <c r="D6" s="1">
         <v>0</v>
       </c>
       <c r="E6" s="1">
-        <v>2646</v>
+        <v>2068</v>
       </c>
       <c r="F6" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -1535,45 +1526,45 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B7" s="2">
-        <v>7.193346977233887</v>
+        <v>5.912818431854248</v>
       </c>
       <c r="C7" s="1">
-        <v>2076</v>
+        <v>1370</v>
       </c>
       <c r="D7" s="1">
-        <v>0</v>
+        <v>864</v>
       </c>
       <c r="E7" s="1">
-        <v>2068</v>
+        <v>1370</v>
       </c>
       <c r="F7" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
       </c>
       <c r="H7" s="1">
-        <v>0</v>
+        <v>864</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B8" s="2">
-        <v>5.599445819854736</v>
+        <v>5.783340454101563</v>
       </c>
       <c r="C8" s="1">
-        <v>1616</v>
+        <v>1340</v>
       </c>
       <c r="D8" s="1">
-        <v>120</v>
+        <v>360</v>
       </c>
       <c r="E8" s="1">
-        <v>1616</v>
+        <v>1340</v>
       </c>
       <c r="F8" s="1">
         <v>0</v>
@@ -1582,24 +1573,24 @@
         <v>0</v>
       </c>
       <c r="H8" s="1">
-        <v>120</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="B9" s="2">
-        <v>4.747054576873779</v>
+        <v>4.298662185668945</v>
       </c>
       <c r="C9" s="1">
-        <v>1370</v>
+        <v>996</v>
       </c>
       <c r="D9" s="1">
-        <v>864</v>
+        <v>0</v>
       </c>
       <c r="E9" s="1">
-        <v>1370</v>
+        <v>996</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
@@ -1608,24 +1599,24 @@
         <v>0</v>
       </c>
       <c r="H9" s="1">
-        <v>864</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B10" s="2">
-        <v>4.643104553222656</v>
+        <v>3.987915515899658</v>
       </c>
       <c r="C10" s="1">
-        <v>1340</v>
+        <v>924</v>
       </c>
       <c r="D10" s="1">
-        <v>360</v>
+        <v>116</v>
       </c>
       <c r="E10" s="1">
-        <v>1340</v>
+        <v>924</v>
       </c>
       <c r="F10" s="1">
         <v>0</v>
@@ -1634,50 +1625,50 @@
         <v>0</v>
       </c>
       <c r="H10" s="1">
-        <v>360</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>3.568953514099121</v>
+        <v>3.685800552368164</v>
       </c>
       <c r="C11" s="1">
-        <v>1030</v>
+        <v>854</v>
       </c>
       <c r="D11" s="1">
-        <v>616</v>
+        <v>8</v>
       </c>
       <c r="E11" s="1">
-        <v>814</v>
+        <v>854</v>
       </c>
       <c r="F11" s="1">
         <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>216</v>
+        <v>0</v>
       </c>
       <c r="H11" s="1">
-        <v>400</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B12" s="2">
-        <v>3.451143503189087</v>
+        <v>2.166594743728638</v>
       </c>
       <c r="C12" s="1">
-        <v>996</v>
+        <v>502</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
       </c>
       <c r="E12" s="1">
-        <v>996</v>
+        <v>502</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
@@ -1691,19 +1682,19 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B13" s="2">
-        <v>2.959112882614136</v>
+        <v>2.080276250839233</v>
       </c>
       <c r="C13" s="1">
-        <v>854</v>
+        <v>482</v>
       </c>
       <c r="D13" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E13" s="1">
-        <v>854</v>
+        <v>482</v>
       </c>
       <c r="F13" s="1">
         <v>0</v>
@@ -1712,50 +1703,50 @@
         <v>0</v>
       </c>
       <c r="H13" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="B14" s="2">
-        <v>1.739431738853455</v>
+        <v>1.847216248512268</v>
       </c>
       <c r="C14" s="1">
-        <v>502</v>
+        <v>428</v>
       </c>
       <c r="D14" s="1">
-        <v>0</v>
+        <v>1024</v>
       </c>
       <c r="E14" s="1">
-        <v>502</v>
+        <v>36</v>
       </c>
       <c r="F14" s="1">
-        <v>0</v>
+        <v>392</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
       </c>
       <c r="H14" s="1">
-        <v>0</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15" s="2">
-        <v>1.670131683349609</v>
+        <v>1.38972806930542</v>
       </c>
       <c r="C15" s="1">
-        <v>482</v>
+        <v>322</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
       </c>
       <c r="E15" s="1">
-        <v>482</v>
+        <v>322</v>
       </c>
       <c r="F15" s="1">
         <v>0</v>
@@ -1769,25 +1760,25 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="B16" s="2">
-        <v>1.524601578712463</v>
+        <v>1.38972806930542</v>
       </c>
       <c r="C16" s="1">
-        <v>440</v>
+        <v>322</v>
       </c>
       <c r="D16" s="1">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="E16" s="1">
-        <v>440</v>
+        <v>106</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="H16" s="1">
         <v>0</v>
@@ -1795,45 +1786,45 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="B17" s="2">
-        <v>1.48302149772644</v>
+        <v>1.320673227310181</v>
       </c>
       <c r="C17" s="1">
-        <v>428</v>
+        <v>306</v>
       </c>
       <c r="D17" s="1">
-        <v>1024</v>
+        <v>0</v>
       </c>
       <c r="E17" s="1">
-        <v>36</v>
+        <v>306</v>
       </c>
       <c r="F17" s="1">
-        <v>392</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
       </c>
       <c r="H17" s="1">
-        <v>1024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B18" s="2">
-        <v>1.060291051864624</v>
+        <v>1.268882155418396</v>
       </c>
       <c r="C18" s="1">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="D18" s="1">
         <v>0</v>
       </c>
       <c r="E18" s="1">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -1847,28 +1838,28 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B19" s="2">
-        <v>1.053361058235169</v>
+        <v>1.186879634857178</v>
       </c>
       <c r="C19" s="1">
-        <v>304</v>
+        <v>275</v>
       </c>
       <c r="D19" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E19" s="1">
-        <v>304</v>
+        <v>270</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H19" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1876,16 +1867,16 @@
         <v>21</v>
       </c>
       <c r="B20" s="2">
-        <v>1.018710970878601</v>
+        <v>0.984031081199646</v>
       </c>
       <c r="C20" s="1">
-        <v>294</v>
+        <v>228</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
       </c>
       <c r="E20" s="1">
-        <v>294</v>
+        <v>228</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
@@ -1899,54 +1890,54 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="B21" s="2">
-        <v>0.9528759717941284</v>
+        <v>0.8545532822608948</v>
       </c>
       <c r="C21" s="1">
-        <v>275</v>
+        <v>198</v>
       </c>
       <c r="D21" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E21" s="1">
-        <v>270</v>
+        <v>198</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
       </c>
       <c r="G21" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H21" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="B22" s="2">
-        <v>0.790020763874054</v>
+        <v>0.841605544090271</v>
       </c>
       <c r="C22" s="1">
-        <v>228</v>
+        <v>195</v>
       </c>
       <c r="D22" s="1">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="E22" s="1">
-        <v>228</v>
+        <v>194</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1954,16 +1945,16 @@
         <v>23</v>
       </c>
       <c r="B23" s="2">
-        <v>0.6860706806182861</v>
+        <v>0.8027622103691101</v>
       </c>
       <c r="C23" s="1">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="D23" s="1">
         <v>0</v>
       </c>
       <c r="E23" s="1">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="F23" s="1">
         <v>0</v>
@@ -1980,7 +1971,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="2">
-        <v>0.644490659236908</v>
+        <v>0.8027622103691101</v>
       </c>
       <c r="C24" s="1">
         <v>186</v>
@@ -2003,19 +1994,19 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="B25" s="2">
-        <v>0.644490659236908</v>
+        <v>0.6732844114303589</v>
       </c>
       <c r="C25" s="1">
-        <v>186</v>
+        <v>156</v>
       </c>
       <c r="D25" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E25" s="1">
-        <v>186</v>
+        <v>156</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
@@ -2024,24 +2015,24 @@
         <v>0</v>
       </c>
       <c r="H25" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="B26" s="2">
-        <v>0.5405405163764954</v>
+        <v>0.4229607284069061</v>
       </c>
       <c r="C26" s="1">
-        <v>156</v>
+        <v>98</v>
       </c>
       <c r="D26" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E26" s="1">
-        <v>156</v>
+        <v>98</v>
       </c>
       <c r="F26" s="1">
         <v>0</v>
@@ -2050,7 +2041,7 @@
         <v>0</v>
       </c>
       <c r="H26" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -2058,16 +2049,16 @@
         <v>26</v>
       </c>
       <c r="B27" s="2">
-        <v>0.3395703434944153</v>
+        <v>0.3193784952163696</v>
       </c>
       <c r="C27" s="1">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="D27" s="1">
         <v>0</v>
       </c>
       <c r="E27" s="1">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="F27" s="1">
         <v>0</v>
@@ -2084,16 +2075,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="2">
-        <v>0.2564102709293366</v>
+        <v>0.2157962918281555</v>
       </c>
       <c r="C28" s="1">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="D28" s="1">
         <v>0</v>
       </c>
       <c r="E28" s="1">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="F28" s="1">
         <v>0</v>
@@ -2110,16 +2101,16 @@
         <v>28</v>
       </c>
       <c r="B29" s="2">
-        <v>0.1732501685619354</v>
+        <v>0.2071644365787506</v>
       </c>
       <c r="C29" s="1">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D29" s="1">
         <v>0</v>
       </c>
       <c r="E29" s="1">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F29" s="1">
         <v>0</v>
@@ -2133,25 +2124,25 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="B30" s="2">
-        <v>0.1663201600313187</v>
+        <v>0.1985325813293457</v>
       </c>
       <c r="C30" s="1">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D30" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E30" s="1">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="F30" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G30" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H30" s="1">
         <v>0</v>
@@ -2159,25 +2150,25 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="B31" s="2">
-        <v>0.1593901664018631</v>
+        <v>0.1640051752328873</v>
       </c>
       <c r="C31" s="1">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D31" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E31" s="1">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="F31" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G31" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H31" s="1">
         <v>0</v>
@@ -2188,16 +2179,16 @@
         <v>30</v>
       </c>
       <c r="B32" s="2">
-        <v>0.1316701322793961</v>
+        <v>0.1553733348846436</v>
       </c>
       <c r="C32" s="1">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D32" s="1">
         <v>0</v>
       </c>
       <c r="E32" s="1">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F32" s="1">
         <v>0</v>
@@ -2214,16 +2205,16 @@
         <v>31</v>
       </c>
       <c r="B33" s="2">
-        <v>0.1247401237487793</v>
+        <v>0.1381096243858337</v>
       </c>
       <c r="C33" s="1">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D33" s="1">
         <v>0</v>
       </c>
       <c r="E33" s="1">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F33" s="1">
         <v>0</v>
@@ -2240,16 +2231,16 @@
         <v>32</v>
       </c>
       <c r="B34" s="2">
-        <v>0.1108801141381264</v>
+        <v>0.1294777691364288</v>
       </c>
       <c r="C34" s="1">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D34" s="1">
         <v>0</v>
       </c>
       <c r="E34" s="1">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F34" s="1">
         <v>0</v>
@@ -2266,7 +2257,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="2">
-        <v>0.1039501056075096</v>
+        <v>0.1294777691364288</v>
       </c>
       <c r="C35" s="1">
         <v>30</v>
@@ -2292,16 +2283,16 @@
         <v>34</v>
       </c>
       <c r="B36" s="2">
-        <v>0.1039501056075096</v>
+        <v>0.03452740609645844</v>
       </c>
       <c r="C36" s="1">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="D36" s="1">
         <v>0</v>
       </c>
       <c r="E36" s="1">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="F36" s="1">
         <v>0</v>
@@ -2318,7 +2309,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="2">
-        <v>0.02772002853453159</v>
+        <v>0.03452740609645844</v>
       </c>
       <c r="C37" s="1">
         <v>8</v>
@@ -2344,16 +2335,16 @@
         <v>36</v>
       </c>
       <c r="B38" s="2">
-        <v>0.02772002853453159</v>
+        <v>0.01726370304822922</v>
       </c>
       <c r="C38" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D38" s="1">
         <v>0</v>
       </c>
       <c r="E38" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F38" s="1">
         <v>0</v>
@@ -2366,60 +2357,34 @@
       </c>
     </row>
     <row r="39" spans="1:8">
-      <c r="A39" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="2">
-        <v>0.0138600142672658</v>
-      </c>
-      <c r="C39" s="1">
-        <v>4</v>
-      </c>
-      <c r="D39" s="1">
-        <v>0</v>
-      </c>
-      <c r="E39" s="1">
-        <v>4</v>
-      </c>
-      <c r="F39" s="1">
-        <v>0</v>
-      </c>
-      <c r="G39" s="1">
-        <v>0</v>
-      </c>
-      <c r="H39" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" t="s">
-        <v>39</v>
-      </c>
-      <c r="B40">
+      <c r="A39" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39">
         <f>SUBTOTAL(109,[flash_percent])</f>
         <v>0</v>
       </c>
-      <c r="C40">
+      <c r="C39">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="D40">
+      <c r="D39">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="E40">
+      <c r="E39">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F40">
+      <c r="F39">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G40">
+      <c r="G39">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H40">
+      <c r="H39">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>

--- a/MDK-ARM/panzer_analysis.xlsx
+++ b/MDK-ARM/panzer_analysis.xlsx
@@ -15,23 +15,26 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="48">
   <si>
     <t>panzer</t>
   </si>
   <si>
+    <t>usart.o</t>
+  </si>
+  <si>
     <t>startup_stm32f405xx.o</t>
   </si>
   <si>
-    <t>usart.o</t>
-  </si>
-  <si>
     <t>tim.o</t>
   </si>
   <si>
     <t>encode.o</t>
   </si>
   <si>
+    <t>bule_tooch.o</t>
+  </si>
+  <si>
     <t>interurp.o</t>
   </si>
   <si>
@@ -83,13 +86,13 @@
     <t>dmul.o</t>
   </si>
   <si>
+    <t>dma.o</t>
+  </si>
+  <si>
     <t>gpio.o</t>
   </si>
   <si>
     <t>depilogue.o</t>
-  </si>
-  <si>
-    <t>dma.o</t>
   </si>
   <si>
     <t>uldiv.o</t>
@@ -245,14 +248,14 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>ram_percent!$A$3:$A$39</c:f>
+              <c:f>ram_percent!$A$3:$A$40</c:f>
               <c:strCache>
-                <c:ptCount val="37"/>
+                <c:ptCount val="38"/>
                 <c:pt idx="0">
+                  <c:v>usart.o</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>startup_stm32f405xx.o</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>usart.o</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>tim.o</c:v>
@@ -261,24 +264,27 @@
                   <c:v>encode.o</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>bule_tooch.o</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>interurp.o</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>control_car.o</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>emm_v5.o</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>stm32f4xx_hal.o</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>stm32f4xx_it.o</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>system_stm32f4xx.o</c:v>
                 </c:pt>
-                <c:pt idx="36">
+                <c:pt idx="37">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -286,41 +292,44 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>ram_percent!$B$3:$B$39</c:f>
+              <c:f>ram_percent!$B$3:$B$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="37"/>
+                <c:ptCount val="38"/>
                 <c:pt idx="0">
-                  <c:v>37.67476272583008</c:v>
+                  <c:v>34.71400451660156</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>31.7880802154541</c:v>
+                  <c:v>33.66206359863281</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>13.24503326416016</c:v>
+                  <c:v>11.83431911468506</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7.947020053863525</c:v>
+                  <c:v>7.100591659545898</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.267844200134277</c:v>
+                  <c:v>4.339250564575195</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.568800687789917</c:v>
+                  <c:v>3.813280820846558</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.7358351945877075</c:v>
+                  <c:v>3.18869161605835</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.3311258256435394</c:v>
+                  <c:v>0.6574621796607971</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.2943340837955475</c:v>
+                  <c:v>0.2958579957485199</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.1471670418977737</c:v>
-                </c:pt>
-                <c:pt idx="36">
+                  <c:v>0.2629848718643189</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.1314924359321594</c:v>
+                </c:pt>
+                <c:pt idx="37">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -388,9 +397,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>flash_percent!$A$3:$A$39</c:f>
+              <c:f>flash_percent!$A$3:$A$40</c:f>
               <c:strCache>
-                <c:ptCount val="37"/>
+                <c:ptCount val="38"/>
                 <c:pt idx="0">
                   <c:v>stm32f4xx_hal_tim.o</c:v>
                 </c:pt>
@@ -401,105 +410,108 @@
                   <c:v>stm32f4xx_hal_rcc.o</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>bule_tooch.o</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>stm32f4xx_hal_dma.o</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>usart.o</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>tim.o</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>stm32f4xx_hal_gpio.o</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>interurp.o</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>stm32f4xx_it.o</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>interurp.o</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>mf_w.l</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>stm32f4xx_hal_cortex.o</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>startup_stm32f405xx.o</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>main.o</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>encode.o</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>stm32f4xx_hal_tim_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>mc_w.l</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>stm32f4xx_hal.o</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
                   <c:v>dmul.o</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="19">
+                  <c:v>dma.o</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>gpio.o</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="21">
                   <c:v>control_car.o</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="22">
                   <c:v>depilogue.o</c:v>
                 </c:pt>
-                <c:pt idx="21">
-                  <c:v>dma.o</c:v>
-                </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="23">
                   <c:v>emm_v5.o</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="24">
                   <c:v>uldiv.o</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="25">
                   <c:v>stm32f4xx_hal_msp.o</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="26">
                   <c:v>dfixui.o</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="27">
                   <c:v>init.o</c:v>
                 </c:pt>
-                <c:pt idx="27">
+                <c:pt idx="28">
                   <c:v>system_stm32f4xx.o</c:v>
                 </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="29">
                   <c:v>f2d.o</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="30">
                   <c:v>memseta.o</c:v>
                 </c:pt>
-                <c:pt idx="30">
+                <c:pt idx="31">
                   <c:v>llushr.o</c:v>
                 </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="32">
                   <c:v>llshl.o</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="33">
                   <c:v>handlers.o</c:v>
                 </c:pt>
-                <c:pt idx="33">
+                <c:pt idx="34">
                   <c:v>entry9a.o</c:v>
                 </c:pt>
-                <c:pt idx="34">
+                <c:pt idx="35">
                   <c:v>entry2.o</c:v>
                 </c:pt>
-                <c:pt idx="35">
+                <c:pt idx="36">
                   <c:v>entry5.o</c:v>
                 </c:pt>
-                <c:pt idx="36">
+                <c:pt idx="37">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -507,119 +519,122 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>flash_percent!$B$3:$B$39</c:f>
+              <c:f>flash_percent!$B$3:$B$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="37"/>
+                <c:ptCount val="38"/>
                 <c:pt idx="0">
-                  <c:v>19.66335868835449</c:v>
+                  <c:v>17.82472610473633</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>16.51273155212402</c:v>
+                  <c:v>14.96870136260986</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>11.41993999481201</c:v>
+                  <c:v>10.35211277008057</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8.959861755371094</c:v>
+                  <c:v>8.169013977050781</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.912818431854248</c:v>
+                  <c:v>8.122065544128418</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.783340454101563</c:v>
+                  <c:v>6.032863616943359</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.298662185668945</c:v>
+                  <c:v>5.242566585540772</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.987915515899658</c:v>
+                  <c:v>3.896713733673096</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.685800552368164</c:v>
+                  <c:v>3.693270683288574</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.166594743728638</c:v>
+                  <c:v>3.615023374557495</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.080276250839233</c:v>
+                  <c:v>1.964006304740906</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.847216248512268</c:v>
+                  <c:v>1.885758996009827</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.38972806930542</c:v>
+                  <c:v>1.674491405487061</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.38972806930542</c:v>
+                  <c:v>1.27543032169342</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.320673227310181</c:v>
+                  <c:v>1.259780883789063</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.268882155418396</c:v>
+                  <c:v>1.197183132171631</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.186879634857178</c:v>
+                  <c:v>1.150234699249268</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.984031081199646</c:v>
+                  <c:v>1.075899839401245</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.8545532822608948</c:v>
+                  <c:v>0.8920187950134277</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.841605544090271</c:v>
+                  <c:v>0.8685445785522461</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.8027622103691101</c:v>
+                  <c:v>0.7746478915214539</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.8027622103691101</c:v>
+                  <c:v>0.762910783290863</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.6732844114303589</c:v>
+                  <c:v>0.7276995182037354</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.4229607284069061</c:v>
+                  <c:v>0.6103286147117615</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.3193784952163696</c:v>
+                  <c:v>0.3834115862846375</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.2157962918281555</c:v>
+                  <c:v>0.2895148694515228</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.2071644365787506</c:v>
+                  <c:v>0.1956181526184082</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.1985325813293457</c:v>
+                  <c:v>0.1877934336662293</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.1640051752328873</c:v>
+                  <c:v>0.1799686998128891</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.1553733348846436</c:v>
+                  <c:v>0.1486697942018509</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.1381096243858337</c:v>
+                  <c:v>0.1408450752496719</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.1294777691364288</c:v>
+                  <c:v>0.1251956224441528</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.1294777691364288</c:v>
+                  <c:v>0.1173708885908127</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.03452740609645844</c:v>
+                  <c:v>0.1173708885908127</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.03452740609645844</c:v>
+                  <c:v>0.03129890561103821</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.01726370304822922</c:v>
+                  <c:v>0.03129890561103821</c:v>
                 </c:pt>
                 <c:pt idx="36">
+                  <c:v>0.0156494528055191</c:v>
+                </c:pt>
+                <c:pt idx="37">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -724,8 +739,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H39" totalsRowCount="1">
-  <autoFilter ref="A2:H38"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H40" totalsRowCount="1">
+  <autoFilter ref="A2:H39"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="ram_percent" totalsRowFunction="sum"/>
@@ -741,8 +756,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H39" totalsRowCount="1">
-  <autoFilter ref="A2:H38"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H40" totalsRowCount="1">
+  <autoFilter ref="A2:H39"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="flash_percent" totalsRowFunction="sum"/>
@@ -1042,7 +1057,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -1055,28 +1070,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1084,25 +1099,25 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>37.67476272583008</v>
+        <v>34.71400451660156</v>
       </c>
       <c r="C3" s="1">
-        <v>1024</v>
+        <v>1056</v>
       </c>
       <c r="D3" s="1">
-        <v>428</v>
+        <v>1542</v>
       </c>
       <c r="E3" s="1">
-        <v>36</v>
+        <v>1542</v>
       </c>
       <c r="F3" s="1">
-        <v>392</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
       </c>
       <c r="H3" s="1">
-        <v>1024</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1110,25 +1125,25 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>31.7880802154541</v>
+        <v>33.66206359863281</v>
       </c>
       <c r="C4" s="1">
-        <v>864</v>
+        <v>1024</v>
       </c>
       <c r="D4" s="1">
-        <v>1370</v>
+        <v>428</v>
       </c>
       <c r="E4" s="1">
-        <v>1370</v>
+        <v>36</v>
       </c>
       <c r="F4" s="1">
-        <v>0</v>
+        <v>392</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
       </c>
       <c r="H4" s="1">
-        <v>864</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1136,7 +1151,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>13.24503326416016</v>
+        <v>11.83431911468506</v>
       </c>
       <c r="C5" s="1">
         <v>360</v>
@@ -1162,7 +1177,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>7.947020053863525</v>
+        <v>7.100591659545898</v>
       </c>
       <c r="C6" s="1">
         <v>216</v>
@@ -1188,16 +1203,16 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>4.267844200134277</v>
+        <v>4.339250564575195</v>
       </c>
       <c r="C7" s="1">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="D7" s="1">
-        <v>924</v>
+        <v>2088</v>
       </c>
       <c r="E7" s="1">
-        <v>924</v>
+        <v>2088</v>
       </c>
       <c r="F7" s="1">
         <v>0</v>
@@ -1206,7 +1221,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="1">
-        <v>116</v>
+        <v>132</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1214,25 +1229,25 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>3.568800687789917</v>
+        <v>3.813280820846558</v>
       </c>
       <c r="C8" s="1">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="D8" s="1">
-        <v>195</v>
+        <v>924</v>
       </c>
       <c r="E8" s="1">
-        <v>194</v>
+        <v>924</v>
       </c>
       <c r="F8" s="1">
         <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" s="1">
-        <v>96</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1240,25 +1255,25 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>0.7358351945877075</v>
+        <v>3.18869161605835</v>
       </c>
       <c r="C9" s="1">
-        <v>20</v>
+        <v>97</v>
       </c>
       <c r="D9" s="1">
-        <v>156</v>
+        <v>195</v>
       </c>
       <c r="E9" s="1">
-        <v>156</v>
+        <v>194</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" s="1">
-        <v>20</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1266,25 +1281,25 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>0.3311258256435394</v>
+        <v>0.6574621796607971</v>
       </c>
       <c r="C10" s="1">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D10" s="1">
-        <v>275</v>
+        <v>156</v>
       </c>
       <c r="E10" s="1">
-        <v>270</v>
+        <v>156</v>
       </c>
       <c r="F10" s="1">
         <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H10" s="1">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1292,25 +1307,25 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>0.2943340837955475</v>
+        <v>0.2958579957485199</v>
       </c>
       <c r="C11" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" s="1">
-        <v>854</v>
+        <v>275</v>
       </c>
       <c r="E11" s="1">
-        <v>854</v>
+        <v>270</v>
       </c>
       <c r="F11" s="1">
         <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H11" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1318,56 +1333,82 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.1471670418977737</v>
+        <v>0.2629848718643189</v>
       </c>
       <c r="C12" s="1">
+        <v>8</v>
+      </c>
+      <c r="D12" s="1">
+        <v>944</v>
+      </c>
+      <c r="E12" s="1">
+        <v>944</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0.1314924359321594</v>
+      </c>
+      <c r="C13" s="1">
         <v>4</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D13" s="1">
         <v>46</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E13" s="1">
         <v>18</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F13" s="1">
         <v>24</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G13" s="1">
         <v>4</v>
       </c>
-      <c r="H12" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" t="s">
-        <v>38</v>
-      </c>
-      <c r="B39">
+      <c r="H13" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40">
         <f>SUBTOTAL(109,[ram_percent])</f>
         <v>0</v>
       </c>
-      <c r="C39">
+      <c r="C40">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="D39">
+      <c r="D40">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="E39">
+      <c r="E40">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F39">
+      <c r="F40">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G39">
+      <c r="G40">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H39">
+      <c r="H40">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>
@@ -1383,7 +1424,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -1396,36 +1437,36 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2" t="s">
         <v>46</v>
-      </c>
-      <c r="C2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G2" t="s">
-        <v>44</v>
-      </c>
-      <c r="H2" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" s="2">
-        <v>19.66335868835449</v>
+        <v>17.82472610473633</v>
       </c>
       <c r="C3" s="1">
         <v>4556</v>
@@ -1448,10 +1489,10 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" s="2">
-        <v>16.51273155212402</v>
+        <v>14.96870136260986</v>
       </c>
       <c r="C4" s="1">
         <v>3826</v>
@@ -1474,10 +1515,10 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="2">
-        <v>11.41993999481201</v>
+        <v>10.35211277008057</v>
       </c>
       <c r="C5" s="1">
         <v>2646</v>
@@ -1500,71 +1541,71 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="B6" s="2">
-        <v>8.959861755371094</v>
+        <v>8.169013977050781</v>
       </c>
       <c r="C6" s="1">
-        <v>2076</v>
+        <v>2088</v>
       </c>
       <c r="D6" s="1">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="E6" s="1">
-        <v>2068</v>
+        <v>2088</v>
       </c>
       <c r="F6" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
       </c>
       <c r="H6" s="1">
-        <v>0</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="B7" s="2">
-        <v>5.912818431854248</v>
+        <v>8.122065544128418</v>
       </c>
       <c r="C7" s="1">
-        <v>1370</v>
+        <v>2076</v>
       </c>
       <c r="D7" s="1">
-        <v>864</v>
+        <v>0</v>
       </c>
       <c r="E7" s="1">
-        <v>1370</v>
+        <v>2068</v>
       </c>
       <c r="F7" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
       </c>
       <c r="H7" s="1">
-        <v>864</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B8" s="2">
-        <v>5.783340454101563</v>
+        <v>6.032863616943359</v>
       </c>
       <c r="C8" s="1">
-        <v>1340</v>
+        <v>1542</v>
       </c>
       <c r="D8" s="1">
-        <v>360</v>
+        <v>1056</v>
       </c>
       <c r="E8" s="1">
-        <v>1340</v>
+        <v>1542</v>
       </c>
       <c r="F8" s="1">
         <v>0</v>
@@ -1573,24 +1614,24 @@
         <v>0</v>
       </c>
       <c r="H8" s="1">
-        <v>360</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B9" s="2">
-        <v>4.298662185668945</v>
+        <v>5.242566585540772</v>
       </c>
       <c r="C9" s="1">
-        <v>996</v>
+        <v>1340</v>
       </c>
       <c r="D9" s="1">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="E9" s="1">
-        <v>996</v>
+        <v>1340</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
@@ -1599,24 +1640,24 @@
         <v>0</v>
       </c>
       <c r="H9" s="1">
-        <v>0</v>
+        <v>360</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="B10" s="2">
-        <v>3.987915515899658</v>
+        <v>3.896713733673096</v>
       </c>
       <c r="C10" s="1">
-        <v>924</v>
+        <v>996</v>
       </c>
       <c r="D10" s="1">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="E10" s="1">
-        <v>924</v>
+        <v>996</v>
       </c>
       <c r="F10" s="1">
         <v>0</v>
@@ -1625,24 +1666,24 @@
         <v>0</v>
       </c>
       <c r="H10" s="1">
-        <v>116</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" s="2">
-        <v>3.685800552368164</v>
+        <v>3.693270683288574</v>
       </c>
       <c r="C11" s="1">
-        <v>854</v>
+        <v>944</v>
       </c>
       <c r="D11" s="1">
         <v>8</v>
       </c>
       <c r="E11" s="1">
-        <v>854</v>
+        <v>944</v>
       </c>
       <c r="F11" s="1">
         <v>0</v>
@@ -1656,19 +1697,19 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B12" s="2">
-        <v>2.166594743728638</v>
+        <v>3.615023374557495</v>
       </c>
       <c r="C12" s="1">
-        <v>502</v>
+        <v>924</v>
       </c>
       <c r="D12" s="1">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="E12" s="1">
-        <v>502</v>
+        <v>924</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
@@ -1677,7 +1718,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="1">
-        <v>0</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1685,16 +1726,16 @@
         <v>17</v>
       </c>
       <c r="B13" s="2">
-        <v>2.080276250839233</v>
+        <v>1.964006304740906</v>
       </c>
       <c r="C13" s="1">
-        <v>482</v>
+        <v>502</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
       </c>
       <c r="E13" s="1">
-        <v>482</v>
+        <v>502</v>
       </c>
       <c r="F13" s="1">
         <v>0</v>
@@ -1708,77 +1749,77 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="B14" s="2">
-        <v>1.847216248512268</v>
+        <v>1.885758996009827</v>
       </c>
       <c r="C14" s="1">
-        <v>428</v>
+        <v>482</v>
       </c>
       <c r="D14" s="1">
-        <v>1024</v>
+        <v>0</v>
       </c>
       <c r="E14" s="1">
-        <v>36</v>
+        <v>482</v>
       </c>
       <c r="F14" s="1">
-        <v>392</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
       </c>
       <c r="H14" s="1">
-        <v>1024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="B15" s="2">
-        <v>1.38972806930542</v>
+        <v>1.674491405487061</v>
       </c>
       <c r="C15" s="1">
-        <v>322</v>
+        <v>428</v>
       </c>
       <c r="D15" s="1">
-        <v>0</v>
+        <v>1024</v>
       </c>
       <c r="E15" s="1">
-        <v>322</v>
+        <v>36</v>
       </c>
       <c r="F15" s="1">
-        <v>0</v>
+        <v>392</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
       </c>
       <c r="H15" s="1">
-        <v>0</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="B16" s="2">
-        <v>1.38972806930542</v>
+        <v>1.27543032169342</v>
       </c>
       <c r="C16" s="1">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="D16" s="1">
-        <v>216</v>
+        <v>0</v>
       </c>
       <c r="E16" s="1">
-        <v>106</v>
+        <v>326</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>216</v>
+        <v>0</v>
       </c>
       <c r="H16" s="1">
         <v>0</v>
@@ -1786,25 +1827,25 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="B17" s="2">
-        <v>1.320673227310181</v>
+        <v>1.259780883789063</v>
       </c>
       <c r="C17" s="1">
-        <v>306</v>
+        <v>322</v>
       </c>
       <c r="D17" s="1">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="E17" s="1">
-        <v>306</v>
+        <v>106</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="H17" s="1">
         <v>0</v>
@@ -1815,16 +1856,16 @@
         <v>20</v>
       </c>
       <c r="B18" s="2">
-        <v>1.268882155418396</v>
+        <v>1.197183132171631</v>
       </c>
       <c r="C18" s="1">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="D18" s="1">
         <v>0</v>
       </c>
       <c r="E18" s="1">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -1838,54 +1879,54 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="B19" s="2">
-        <v>1.186879634857178</v>
+        <v>1.150234699249268</v>
       </c>
       <c r="C19" s="1">
-        <v>275</v>
+        <v>294</v>
       </c>
       <c r="D19" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E19" s="1">
-        <v>270</v>
+        <v>294</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
       </c>
       <c r="G19" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H19" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="B20" s="2">
-        <v>0.984031081199646</v>
+        <v>1.075899839401245</v>
       </c>
       <c r="C20" s="1">
-        <v>228</v>
+        <v>275</v>
       </c>
       <c r="D20" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E20" s="1">
-        <v>228</v>
+        <v>270</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H20" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1893,16 +1934,16 @@
         <v>22</v>
       </c>
       <c r="B21" s="2">
-        <v>0.8545532822608948</v>
+        <v>0.8920187950134277</v>
       </c>
       <c r="C21" s="1">
-        <v>198</v>
+        <v>228</v>
       </c>
       <c r="D21" s="1">
         <v>0</v>
       </c>
       <c r="E21" s="1">
-        <v>198</v>
+        <v>228</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
@@ -1916,45 +1957,45 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="B22" s="2">
-        <v>0.841605544090271</v>
+        <v>0.8685445785522461</v>
       </c>
       <c r="C22" s="1">
-        <v>195</v>
+        <v>222</v>
       </c>
       <c r="D22" s="1">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="E22" s="1">
-        <v>194</v>
+        <v>222</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
       </c>
       <c r="G22" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" s="1">
-        <v>96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B23" s="2">
-        <v>0.8027622103691101</v>
+        <v>0.7746478915214539</v>
       </c>
       <c r="C23" s="1">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="D23" s="1">
         <v>0</v>
       </c>
       <c r="E23" s="1">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="F23" s="1">
         <v>0</v>
@@ -1968,45 +2009,45 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="B24" s="2">
-        <v>0.8027622103691101</v>
+        <v>0.762910783290863</v>
       </c>
       <c r="C24" s="1">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="D24" s="1">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="E24" s="1">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="F24" s="1">
         <v>0</v>
       </c>
       <c r="G24" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="B25" s="2">
-        <v>0.6732844114303589</v>
+        <v>0.7276995182037354</v>
       </c>
       <c r="C25" s="1">
-        <v>156</v>
+        <v>186</v>
       </c>
       <c r="D25" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E25" s="1">
-        <v>156</v>
+        <v>186</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
@@ -2015,24 +2056,24 @@
         <v>0</v>
       </c>
       <c r="H25" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="B26" s="2">
-        <v>0.4229607284069061</v>
+        <v>0.6103286147117615</v>
       </c>
       <c r="C26" s="1">
-        <v>98</v>
+        <v>156</v>
       </c>
       <c r="D26" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E26" s="1">
-        <v>98</v>
+        <v>156</v>
       </c>
       <c r="F26" s="1">
         <v>0</v>
@@ -2041,7 +2082,7 @@
         <v>0</v>
       </c>
       <c r="H26" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -2049,16 +2090,16 @@
         <v>26</v>
       </c>
       <c r="B27" s="2">
-        <v>0.3193784952163696</v>
+        <v>0.3834115862846375</v>
       </c>
       <c r="C27" s="1">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="D27" s="1">
         <v>0</v>
       </c>
       <c r="E27" s="1">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="F27" s="1">
         <v>0</v>
@@ -2075,16 +2116,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="2">
-        <v>0.2157962918281555</v>
+        <v>0.2895148694515228</v>
       </c>
       <c r="C28" s="1">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="D28" s="1">
         <v>0</v>
       </c>
       <c r="E28" s="1">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="F28" s="1">
         <v>0</v>
@@ -2101,16 +2142,16 @@
         <v>28</v>
       </c>
       <c r="B29" s="2">
-        <v>0.2071644365787506</v>
+        <v>0.1956181526184082</v>
       </c>
       <c r="C29" s="1">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D29" s="1">
         <v>0</v>
       </c>
       <c r="E29" s="1">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F29" s="1">
         <v>0</v>
@@ -2124,25 +2165,25 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="B30" s="2">
-        <v>0.1985325813293457</v>
+        <v>0.1877934336662293</v>
       </c>
       <c r="C30" s="1">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D30" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E30" s="1">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="F30" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G30" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H30" s="1">
         <v>0</v>
@@ -2150,25 +2191,25 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="B31" s="2">
-        <v>0.1640051752328873</v>
+        <v>0.1799686998128891</v>
       </c>
       <c r="C31" s="1">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="D31" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E31" s="1">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="F31" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G31" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H31" s="1">
         <v>0</v>
@@ -2179,16 +2220,16 @@
         <v>30</v>
       </c>
       <c r="B32" s="2">
-        <v>0.1553733348846436</v>
+        <v>0.1486697942018509</v>
       </c>
       <c r="C32" s="1">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D32" s="1">
         <v>0</v>
       </c>
       <c r="E32" s="1">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F32" s="1">
         <v>0</v>
@@ -2205,16 +2246,16 @@
         <v>31</v>
       </c>
       <c r="B33" s="2">
-        <v>0.1381096243858337</v>
+        <v>0.1408450752496719</v>
       </c>
       <c r="C33" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D33" s="1">
         <v>0</v>
       </c>
       <c r="E33" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F33" s="1">
         <v>0</v>
@@ -2231,16 +2272,16 @@
         <v>32</v>
       </c>
       <c r="B34" s="2">
-        <v>0.1294777691364288</v>
+        <v>0.1251956224441528</v>
       </c>
       <c r="C34" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D34" s="1">
         <v>0</v>
       </c>
       <c r="E34" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F34" s="1">
         <v>0</v>
@@ -2257,7 +2298,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="2">
-        <v>0.1294777691364288</v>
+        <v>0.1173708885908127</v>
       </c>
       <c r="C35" s="1">
         <v>30</v>
@@ -2283,16 +2324,16 @@
         <v>34</v>
       </c>
       <c r="B36" s="2">
-        <v>0.03452740609645844</v>
+        <v>0.1173708885908127</v>
       </c>
       <c r="C36" s="1">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="D36" s="1">
         <v>0</v>
       </c>
       <c r="E36" s="1">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F36" s="1">
         <v>0</v>
@@ -2309,7 +2350,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="2">
-        <v>0.03452740609645844</v>
+        <v>0.03129890561103821</v>
       </c>
       <c r="C37" s="1">
         <v>8</v>
@@ -2335,56 +2376,82 @@
         <v>36</v>
       </c>
       <c r="B38" s="2">
-        <v>0.01726370304822922</v>
+        <v>0.03129890561103821</v>
       </c>
       <c r="C38" s="1">
+        <v>8</v>
+      </c>
+      <c r="D38" s="1">
+        <v>0</v>
+      </c>
+      <c r="E38" s="1">
+        <v>8</v>
+      </c>
+      <c r="F38" s="1">
+        <v>0</v>
+      </c>
+      <c r="G38" s="1">
+        <v>0</v>
+      </c>
+      <c r="H38" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="2">
+        <v>0.0156494528055191</v>
+      </c>
+      <c r="C39" s="1">
         <v>4</v>
       </c>
-      <c r="D38" s="1">
-        <v>0</v>
-      </c>
-      <c r="E38" s="1">
+      <c r="D39" s="1">
+        <v>0</v>
+      </c>
+      <c r="E39" s="1">
         <v>4</v>
       </c>
-      <c r="F38" s="1">
-        <v>0</v>
-      </c>
-      <c r="G38" s="1">
-        <v>0</v>
-      </c>
-      <c r="H38" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" t="s">
-        <v>38</v>
-      </c>
-      <c r="B39">
+      <c r="F39" s="1">
+        <v>0</v>
+      </c>
+      <c r="G39" s="1">
+        <v>0</v>
+      </c>
+      <c r="H39" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40">
         <f>SUBTOTAL(109,[flash_percent])</f>
         <v>0</v>
       </c>
-      <c r="C39">
+      <c r="C40">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="D39">
+      <c r="D40">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="E39">
+      <c r="E40">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F39">
+      <c r="F40">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G39">
+      <c r="G40">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H39">
+      <c r="H40">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>

--- a/MDK-ARM/panzer_analysis.xlsx
+++ b/MDK-ARM/panzer_analysis.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="50">
   <si>
     <t>panzer</t>
   </si>
@@ -26,12 +26,12 @@
     <t>startup_stm32f405xx.o</t>
   </si>
   <si>
+    <t>encode.o</t>
+  </si>
+  <si>
     <t>tim.o</t>
   </si>
   <si>
-    <t>encode.o</t>
-  </si>
-  <si>
     <t>bule_tooch.o</t>
   </si>
   <si>
@@ -74,6 +74,9 @@
     <t>stm32f4xx_hal_cortex.o</t>
   </si>
   <si>
+    <t>pid.o</t>
+  </si>
+  <si>
     <t>main.o</t>
   </si>
   <si>
@@ -81,6 +84,9 @@
   </si>
   <si>
     <t>mc_w.l</t>
+  </si>
+  <si>
+    <t>bule_car_control.o</t>
   </si>
   <si>
     <t>dmul.o</t>
@@ -248,9 +254,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>ram_percent!$A$3:$A$40</c:f>
+              <c:f>ram_percent!$A$3:$A$42</c:f>
               <c:strCache>
-                <c:ptCount val="38"/>
+                <c:ptCount val="40"/>
                 <c:pt idx="0">
                   <c:v>usart.o</c:v>
                 </c:pt>
@@ -258,10 +264,10 @@
                   <c:v>startup_stm32f405xx.o</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>encode.o</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>tim.o</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>encode.o</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>bule_tooch.o</c:v>
@@ -284,7 +290,7 @@
                 <c:pt idx="10">
                   <c:v>system_stm32f4xx.o</c:v>
                 </c:pt>
-                <c:pt idx="37">
+                <c:pt idx="39">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -292,44 +298,44 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>ram_percent!$B$3:$B$40</c:f>
+              <c:f>ram_percent!$B$3:$B$42</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="38"/>
+                <c:ptCount val="40"/>
                 <c:pt idx="0">
-                  <c:v>34.71400451660156</c:v>
+                  <c:v>30.63533592224121</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>33.66206359863281</c:v>
+                  <c:v>29.70699119567871</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>11.83431911468506</c:v>
+                  <c:v>17.8706111907959</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7.100591659545898</c:v>
+                  <c:v>10.44386386871338</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.339250564575195</c:v>
+                  <c:v>3.829416990280151</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.813280820846558</c:v>
+                  <c:v>3.36524510383606</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.18869161605835</c:v>
+                  <c:v>2.959094762802124</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.6574621796607971</c:v>
+                  <c:v>0.5802146792411804</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.2958579957485199</c:v>
+                  <c:v>0.2610965967178345</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.2629848718643189</c:v>
+                  <c:v>0.2320858687162399</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.1314924359321594</c:v>
-                </c:pt>
-                <c:pt idx="37">
+                  <c:v>0.11604293435812</c:v>
+                </c:pt>
+                <c:pt idx="39">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -397,9 +403,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>flash_percent!$A$3:$A$40</c:f>
+              <c:f>flash_percent!$A$3:$A$42</c:f>
               <c:strCache>
-                <c:ptCount val="38"/>
+                <c:ptCount val="40"/>
                 <c:pt idx="0">
                   <c:v>stm32f4xx_hal_tim.o</c:v>
                 </c:pt>
@@ -422,96 +428,102 @@
                   <c:v>tim.o</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>encode.o</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>stm32f4xx_hal_gpio.o</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>stm32f4xx_it.o</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>interurp.o</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
+                  <c:v>control_car.o</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>mf_w.l</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="13">
                   <c:v>stm32f4xx_hal_cortex.o</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="14">
+                  <c:v>pid.o</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>startup_stm32f405xx.o</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="16">
                   <c:v>main.o</c:v>
                 </c:pt>
-                <c:pt idx="14">
-                  <c:v>encode.o</c:v>
-                </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="17">
                   <c:v>stm32f4xx_hal_tim_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="18">
                   <c:v>mc_w.l</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="19">
                   <c:v>stm32f4xx_hal.o</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="20">
+                  <c:v>bule_car_control.o</c:v>
+                </c:pt>
+                <c:pt idx="21">
                   <c:v>dmul.o</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="22">
                   <c:v>dma.o</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="23">
                   <c:v>gpio.o</c:v>
                 </c:pt>
-                <c:pt idx="21">
-                  <c:v>control_car.o</c:v>
-                </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="24">
                   <c:v>depilogue.o</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="25">
                   <c:v>emm_v5.o</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="26">
                   <c:v>uldiv.o</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="27">
                   <c:v>stm32f4xx_hal_msp.o</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="28">
                   <c:v>dfixui.o</c:v>
                 </c:pt>
-                <c:pt idx="27">
+                <c:pt idx="29">
                   <c:v>init.o</c:v>
                 </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="30">
                   <c:v>system_stm32f4xx.o</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="31">
                   <c:v>f2d.o</c:v>
                 </c:pt>
-                <c:pt idx="30">
+                <c:pt idx="32">
                   <c:v>memseta.o</c:v>
                 </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="33">
                   <c:v>llushr.o</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="34">
                   <c:v>llshl.o</c:v>
                 </c:pt>
-                <c:pt idx="33">
+                <c:pt idx="35">
                   <c:v>handlers.o</c:v>
                 </c:pt>
-                <c:pt idx="34">
+                <c:pt idx="36">
                   <c:v>entry9a.o</c:v>
                 </c:pt>
-                <c:pt idx="35">
+                <c:pt idx="37">
                   <c:v>entry2.o</c:v>
                 </c:pt>
-                <c:pt idx="36">
+                <c:pt idx="38">
                   <c:v>entry5.o</c:v>
                 </c:pt>
-                <c:pt idx="37">
+                <c:pt idx="39">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -519,122 +531,128 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>flash_percent!$B$3:$B$40</c:f>
+              <c:f>flash_percent!$B$3:$B$42</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="38"/>
+                <c:ptCount val="40"/>
                 <c:pt idx="0">
-                  <c:v>17.82472610473633</c:v>
+                  <c:v>16.46667671203613</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>14.96870136260986</c:v>
+                  <c:v>13.82824897766113</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>10.35211277008057</c:v>
+                  <c:v>9.563394546508789</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8.169013977050781</c:v>
+                  <c:v>7.597224235534668</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>8.122065544128418</c:v>
+                  <c:v>7.503252983093262</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6.032863616943359</c:v>
+                  <c:v>5.573225498199463</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5.242566585540772</c:v>
+                  <c:v>4.843140125274658</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.896713733673096</c:v>
+                  <c:v>3.72271203994751</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.693270683288574</c:v>
+                  <c:v>3.599826574325562</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.615023374557495</c:v>
+                  <c:v>3.41188383102417</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.964006304740906</c:v>
+                  <c:v>3.339598178863525</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.885758996009827</c:v>
+                  <c:v>3.24924111366272</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.674491405487061</c:v>
+                  <c:v>1.814370393753052</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.27543032169342</c:v>
+                  <c:v>1.742084741592407</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.259780883789063</c:v>
+                  <c:v>1.590284824371338</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.197183132171631</c:v>
+                  <c:v>1.546913385391235</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.150234699249268</c:v>
+                  <c:v>1.178256511688232</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.075899839401245</c:v>
+                  <c:v>1.105970740318298</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.8920187950134277</c:v>
+                  <c:v>1.062599420547485</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.8685445785522461</c:v>
+                  <c:v>0.9939280152320862</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.7746478915214539</c:v>
+                  <c:v>0.874656617641449</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.762910783290863</c:v>
+                  <c:v>0.8240566849708557</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.7276995182037354</c:v>
+                  <c:v>0.8023709654808044</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.6103286147117615</c:v>
+                  <c:v>0.7156281471252441</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.3834115862846375</c:v>
+                  <c:v>0.6722567677497864</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.2895148694515228</c:v>
+                  <c:v>0.5638282299041748</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.1956181526184082</c:v>
+                  <c:v>0.3541997969150543</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.1877934336662293</c:v>
+                  <c:v>0.267456978559494</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.1799686998128891</c:v>
+                  <c:v>0.1807141751050949</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.1486697942018509</c:v>
+                  <c:v>0.1734856218099594</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.1408450752496719</c:v>
+                  <c:v>0.1662570536136627</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.1251956224441528</c:v>
+                  <c:v>0.137342780828476</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.1173708885908127</c:v>
+                  <c:v>0.1301142126321793</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.1173708885908127</c:v>
+                  <c:v>0.1156570762395859</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.03129890561103821</c:v>
+                  <c:v>0.1084285080432892</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.03129890561103821</c:v>
+                  <c:v>0.1084285080432892</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.0156494528055191</c:v>
+                  <c:v>0.02891426905989647</c:v>
                 </c:pt>
                 <c:pt idx="37">
+                  <c:v>0.02891426905989647</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.01445713452994824</c:v>
+                </c:pt>
+                <c:pt idx="39">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -739,8 +757,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H40" totalsRowCount="1">
-  <autoFilter ref="A2:H39"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H42" totalsRowCount="1">
+  <autoFilter ref="A2:H41"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="ram_percent" totalsRowFunction="sum"/>
@@ -756,8 +774,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H40" totalsRowCount="1">
-  <autoFilter ref="A2:H39"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H42" totalsRowCount="1">
+  <autoFilter ref="A2:H41"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="flash_percent" totalsRowFunction="sum"/>
@@ -1057,7 +1075,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -1070,28 +1088,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1099,7 +1117,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>34.71400451660156</v>
+        <v>30.63533592224121</v>
       </c>
       <c r="C3" s="1">
         <v>1056</v>
@@ -1125,7 +1143,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>33.66206359863281</v>
+        <v>29.70699119567871</v>
       </c>
       <c r="C4" s="1">
         <v>1024</v>
@@ -1151,25 +1169,25 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>11.83431911468506</v>
+        <v>17.8706111907959</v>
       </c>
       <c r="C5" s="1">
-        <v>360</v>
+        <v>616</v>
       </c>
       <c r="D5" s="1">
-        <v>1340</v>
+        <v>1030</v>
       </c>
       <c r="E5" s="1">
-        <v>1340</v>
+        <v>814</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="H5" s="1">
-        <v>360</v>
+        <v>400</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1177,25 +1195,25 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>7.100591659545898</v>
+        <v>10.44386386871338</v>
       </c>
       <c r="C6" s="1">
-        <v>216</v>
+        <v>360</v>
       </c>
       <c r="D6" s="1">
-        <v>322</v>
+        <v>1340</v>
       </c>
       <c r="E6" s="1">
-        <v>106</v>
+        <v>1340</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>216</v>
+        <v>0</v>
       </c>
       <c r="H6" s="1">
-        <v>0</v>
+        <v>360</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1203,16 +1221,16 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>4.339250564575195</v>
+        <v>3.829416990280151</v>
       </c>
       <c r="C7" s="1">
         <v>132</v>
       </c>
       <c r="D7" s="1">
-        <v>2088</v>
+        <v>2102</v>
       </c>
       <c r="E7" s="1">
-        <v>2088</v>
+        <v>2102</v>
       </c>
       <c r="F7" s="1">
         <v>0</v>
@@ -1229,7 +1247,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>3.813280820846558</v>
+        <v>3.36524510383606</v>
       </c>
       <c r="C8" s="1">
         <v>116</v>
@@ -1255,16 +1273,16 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>3.18869161605835</v>
+        <v>2.959094762802124</v>
       </c>
       <c r="C9" s="1">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D9" s="1">
-        <v>195</v>
+        <v>899</v>
       </c>
       <c r="E9" s="1">
-        <v>194</v>
+        <v>898</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
@@ -1273,7 +1291,7 @@
         <v>1</v>
       </c>
       <c r="H9" s="1">
-        <v>96</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1281,7 +1299,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>0.6574621796607971</v>
+        <v>0.5802146792411804</v>
       </c>
       <c r="C10" s="1">
         <v>20</v>
@@ -1307,7 +1325,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>0.2958579957485199</v>
+        <v>0.2610965967178345</v>
       </c>
       <c r="C11" s="1">
         <v>9</v>
@@ -1333,7 +1351,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.2629848718643189</v>
+        <v>0.2320858687162399</v>
       </c>
       <c r="C12" s="1">
         <v>8</v>
@@ -1359,7 +1377,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.1314924359321594</v>
+        <v>0.11604293435812</v>
       </c>
       <c r="C13" s="1">
         <v>4</v>
@@ -1380,35 +1398,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:8">
-      <c r="A40" t="s">
-        <v>39</v>
-      </c>
-      <c r="B40">
+    <row r="42" spans="1:8">
+      <c r="A42" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42">
         <f>SUBTOTAL(109,[ram_percent])</f>
         <v>0</v>
       </c>
-      <c r="C40">
+      <c r="C42">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="D40">
+      <c r="D42">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="E40">
+      <c r="E42">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F40">
+      <c r="F42">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G40">
+      <c r="G42">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H40">
+      <c r="H42">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>
@@ -1424,7 +1442,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -1437,28 +1455,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G2" t="s">
         <v>47</v>
       </c>
-      <c r="C2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G2" t="s">
-        <v>45</v>
-      </c>
       <c r="H2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1466,7 +1484,7 @@
         <v>12</v>
       </c>
       <c r="B3" s="2">
-        <v>17.82472610473633</v>
+        <v>16.46667671203613</v>
       </c>
       <c r="C3" s="1">
         <v>4556</v>
@@ -1492,7 +1510,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="2">
-        <v>14.96870136260986</v>
+        <v>13.82824897766113</v>
       </c>
       <c r="C4" s="1">
         <v>3826</v>
@@ -1518,7 +1536,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="2">
-        <v>10.35211277008057</v>
+        <v>9.563394546508789</v>
       </c>
       <c r="C5" s="1">
         <v>2646</v>
@@ -1544,16 +1562,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="2">
-        <v>8.169013977050781</v>
+        <v>7.597224235534668</v>
       </c>
       <c r="C6" s="1">
-        <v>2088</v>
+        <v>2102</v>
       </c>
       <c r="D6" s="1">
         <v>132</v>
       </c>
       <c r="E6" s="1">
-        <v>2088</v>
+        <v>2102</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
@@ -1570,7 +1588,7 @@
         <v>15</v>
       </c>
       <c r="B7" s="2">
-        <v>8.122065544128418</v>
+        <v>7.503252983093262</v>
       </c>
       <c r="C7" s="1">
         <v>2076</v>
@@ -1596,7 +1614,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="2">
-        <v>6.032863616943359</v>
+        <v>5.573225498199463</v>
       </c>
       <c r="C8" s="1">
         <v>1542</v>
@@ -1619,10 +1637,10 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B9" s="2">
-        <v>5.242566585540772</v>
+        <v>4.843140125274658</v>
       </c>
       <c r="C9" s="1">
         <v>1340</v>
@@ -1645,45 +1663,45 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B10" s="2">
-        <v>3.896713733673096</v>
+        <v>3.72271203994751</v>
       </c>
       <c r="C10" s="1">
-        <v>996</v>
+        <v>1030</v>
       </c>
       <c r="D10" s="1">
-        <v>0</v>
+        <v>616</v>
       </c>
       <c r="E10" s="1">
-        <v>996</v>
+        <v>814</v>
       </c>
       <c r="F10" s="1">
         <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="H10" s="1">
-        <v>0</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B11" s="2">
-        <v>3.693270683288574</v>
+        <v>3.599826574325562</v>
       </c>
       <c r="C11" s="1">
-        <v>944</v>
+        <v>996</v>
       </c>
       <c r="D11" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E11" s="1">
-        <v>944</v>
+        <v>996</v>
       </c>
       <c r="F11" s="1">
         <v>0</v>
@@ -1692,24 +1710,24 @@
         <v>0</v>
       </c>
       <c r="H11" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>3.615023374557495</v>
+        <v>3.41188383102417</v>
       </c>
       <c r="C12" s="1">
-        <v>924</v>
+        <v>944</v>
       </c>
       <c r="D12" s="1">
-        <v>116</v>
+        <v>8</v>
       </c>
       <c r="E12" s="1">
-        <v>924</v>
+        <v>944</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
@@ -1718,24 +1736,24 @@
         <v>0</v>
       </c>
       <c r="H12" s="1">
-        <v>116</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="B13" s="2">
-        <v>1.964006304740906</v>
+        <v>3.339598178863525</v>
       </c>
       <c r="C13" s="1">
-        <v>502</v>
+        <v>924</v>
       </c>
       <c r="D13" s="1">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="E13" s="1">
-        <v>502</v>
+        <v>924</v>
       </c>
       <c r="F13" s="1">
         <v>0</v>
@@ -1744,76 +1762,76 @@
         <v>0</v>
       </c>
       <c r="H13" s="1">
-        <v>0</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="B14" s="2">
-        <v>1.885758996009827</v>
+        <v>3.24924111366272</v>
       </c>
       <c r="C14" s="1">
-        <v>482</v>
+        <v>899</v>
       </c>
       <c r="D14" s="1">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="E14" s="1">
-        <v>482</v>
+        <v>898</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" s="1">
-        <v>0</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B15" s="2">
-        <v>1.674491405487061</v>
+        <v>1.814370393753052</v>
       </c>
       <c r="C15" s="1">
-        <v>428</v>
+        <v>502</v>
       </c>
       <c r="D15" s="1">
-        <v>1024</v>
+        <v>0</v>
       </c>
       <c r="E15" s="1">
-        <v>36</v>
+        <v>502</v>
       </c>
       <c r="F15" s="1">
-        <v>392</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
       </c>
       <c r="H15" s="1">
-        <v>1024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" s="2">
-        <v>1.27543032169342</v>
+        <v>1.742084741592407</v>
       </c>
       <c r="C16" s="1">
-        <v>326</v>
+        <v>482</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
       </c>
       <c r="E16" s="1">
-        <v>326</v>
+        <v>482</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
@@ -1827,25 +1845,25 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="B17" s="2">
-        <v>1.259780883789063</v>
+        <v>1.590284824371338</v>
       </c>
       <c r="C17" s="1">
-        <v>322</v>
+        <v>440</v>
       </c>
       <c r="D17" s="1">
-        <v>216</v>
+        <v>0</v>
       </c>
       <c r="E17" s="1">
-        <v>106</v>
+        <v>440</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>216</v>
+        <v>0</v>
       </c>
       <c r="H17" s="1">
         <v>0</v>
@@ -1853,45 +1871,45 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="B18" s="2">
-        <v>1.197183132171631</v>
+        <v>1.546913385391235</v>
       </c>
       <c r="C18" s="1">
-        <v>306</v>
+        <v>428</v>
       </c>
       <c r="D18" s="1">
-        <v>0</v>
+        <v>1024</v>
       </c>
       <c r="E18" s="1">
-        <v>306</v>
+        <v>36</v>
       </c>
       <c r="F18" s="1">
-        <v>0</v>
+        <v>392</v>
       </c>
       <c r="G18" s="1">
         <v>0</v>
       </c>
       <c r="H18" s="1">
-        <v>0</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B19" s="2">
-        <v>1.150234699249268</v>
+        <v>1.178256511688232</v>
       </c>
       <c r="C19" s="1">
-        <v>294</v>
+        <v>326</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
       </c>
       <c r="E19" s="1">
-        <v>294</v>
+        <v>326</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
@@ -1905,28 +1923,28 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="B20" s="2">
-        <v>1.075899839401245</v>
+        <v>1.105970740318298</v>
       </c>
       <c r="C20" s="1">
-        <v>275</v>
+        <v>306</v>
       </c>
       <c r="D20" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E20" s="1">
-        <v>270</v>
+        <v>306</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H20" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1934,16 +1952,16 @@
         <v>22</v>
       </c>
       <c r="B21" s="2">
-        <v>0.8920187950134277</v>
+        <v>1.062599420547485</v>
       </c>
       <c r="C21" s="1">
-        <v>228</v>
+        <v>294</v>
       </c>
       <c r="D21" s="1">
         <v>0</v>
       </c>
       <c r="E21" s="1">
-        <v>228</v>
+        <v>294</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
@@ -1957,45 +1975,45 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="B22" s="2">
-        <v>0.8685445785522461</v>
+        <v>0.9939280152320862</v>
       </c>
       <c r="C22" s="1">
-        <v>222</v>
+        <v>275</v>
       </c>
       <c r="D22" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E22" s="1">
-        <v>222</v>
+        <v>270</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H22" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B23" s="2">
-        <v>0.7746478915214539</v>
+        <v>0.874656617641449</v>
       </c>
       <c r="C23" s="1">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="D23" s="1">
         <v>0</v>
       </c>
       <c r="E23" s="1">
-        <v>198</v>
+        <v>242</v>
       </c>
       <c r="F23" s="1">
         <v>0</v>
@@ -2009,28 +2027,28 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="B24" s="2">
-        <v>0.762910783290863</v>
+        <v>0.8240566849708557</v>
       </c>
       <c r="C24" s="1">
-        <v>195</v>
+        <v>228</v>
       </c>
       <c r="D24" s="1">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="E24" s="1">
-        <v>194</v>
+        <v>228</v>
       </c>
       <c r="F24" s="1">
         <v>0</v>
       </c>
       <c r="G24" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" s="1">
-        <v>96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -2038,16 +2056,16 @@
         <v>25</v>
       </c>
       <c r="B25" s="2">
-        <v>0.7276995182037354</v>
+        <v>0.8023709654808044</v>
       </c>
       <c r="C25" s="1">
-        <v>186</v>
+        <v>222</v>
       </c>
       <c r="D25" s="1">
         <v>0</v>
       </c>
       <c r="E25" s="1">
-        <v>186</v>
+        <v>222</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
@@ -2061,19 +2079,19 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="B26" s="2">
-        <v>0.6103286147117615</v>
+        <v>0.7156281471252441</v>
       </c>
       <c r="C26" s="1">
-        <v>156</v>
+        <v>198</v>
       </c>
       <c r="D26" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E26" s="1">
-        <v>156</v>
+        <v>198</v>
       </c>
       <c r="F26" s="1">
         <v>0</v>
@@ -2082,24 +2100,24 @@
         <v>0</v>
       </c>
       <c r="H26" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B27" s="2">
-        <v>0.3834115862846375</v>
+        <v>0.6722567677497864</v>
       </c>
       <c r="C27" s="1">
-        <v>98</v>
+        <v>186</v>
       </c>
       <c r="D27" s="1">
         <v>0</v>
       </c>
       <c r="E27" s="1">
-        <v>98</v>
+        <v>186</v>
       </c>
       <c r="F27" s="1">
         <v>0</v>
@@ -2113,19 +2131,19 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="B28" s="2">
-        <v>0.2895148694515228</v>
+        <v>0.5638282299041748</v>
       </c>
       <c r="C28" s="1">
-        <v>74</v>
+        <v>156</v>
       </c>
       <c r="D28" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E28" s="1">
-        <v>74</v>
+        <v>156</v>
       </c>
       <c r="F28" s="1">
         <v>0</v>
@@ -2134,7 +2152,7 @@
         <v>0</v>
       </c>
       <c r="H28" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -2142,16 +2160,16 @@
         <v>28</v>
       </c>
       <c r="B29" s="2">
-        <v>0.1956181526184082</v>
+        <v>0.3541997969150543</v>
       </c>
       <c r="C29" s="1">
-        <v>50</v>
+        <v>98</v>
       </c>
       <c r="D29" s="1">
         <v>0</v>
       </c>
       <c r="E29" s="1">
-        <v>50</v>
+        <v>98</v>
       </c>
       <c r="F29" s="1">
         <v>0</v>
@@ -2168,16 +2186,16 @@
         <v>29</v>
       </c>
       <c r="B30" s="2">
-        <v>0.1877934336662293</v>
+        <v>0.267456978559494</v>
       </c>
       <c r="C30" s="1">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="D30" s="1">
         <v>0</v>
       </c>
       <c r="E30" s="1">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="F30" s="1">
         <v>0</v>
@@ -2191,25 +2209,25 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="B31" s="2">
-        <v>0.1799686998128891</v>
+        <v>0.1807141751050949</v>
       </c>
       <c r="C31" s="1">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D31" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E31" s="1">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="F31" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G31" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H31" s="1">
         <v>0</v>
@@ -2217,19 +2235,19 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B32" s="2">
-        <v>0.1486697942018509</v>
+        <v>0.1734856218099594</v>
       </c>
       <c r="C32" s="1">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="D32" s="1">
         <v>0</v>
       </c>
       <c r="E32" s="1">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F32" s="1">
         <v>0</v>
@@ -2243,25 +2261,25 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="B33" s="2">
-        <v>0.1408450752496719</v>
+        <v>0.1662570536136627</v>
       </c>
       <c r="C33" s="1">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="D33" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E33" s="1">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F33" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G33" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H33" s="1">
         <v>0</v>
@@ -2272,16 +2290,16 @@
         <v>32</v>
       </c>
       <c r="B34" s="2">
-        <v>0.1251956224441528</v>
+        <v>0.137342780828476</v>
       </c>
       <c r="C34" s="1">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D34" s="1">
         <v>0</v>
       </c>
       <c r="E34" s="1">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F34" s="1">
         <v>0</v>
@@ -2298,16 +2316,16 @@
         <v>33</v>
       </c>
       <c r="B35" s="2">
-        <v>0.1173708885908127</v>
+        <v>0.1301142126321793</v>
       </c>
       <c r="C35" s="1">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D35" s="1">
         <v>0</v>
       </c>
       <c r="E35" s="1">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F35" s="1">
         <v>0</v>
@@ -2324,16 +2342,16 @@
         <v>34</v>
       </c>
       <c r="B36" s="2">
-        <v>0.1173708885908127</v>
+        <v>0.1156570762395859</v>
       </c>
       <c r="C36" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D36" s="1">
         <v>0</v>
       </c>
       <c r="E36" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F36" s="1">
         <v>0</v>
@@ -2350,16 +2368,16 @@
         <v>35</v>
       </c>
       <c r="B37" s="2">
-        <v>0.03129890561103821</v>
+        <v>0.1084285080432892</v>
       </c>
       <c r="C37" s="1">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="D37" s="1">
         <v>0</v>
       </c>
       <c r="E37" s="1">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F37" s="1">
         <v>0</v>
@@ -2376,16 +2394,16 @@
         <v>36</v>
       </c>
       <c r="B38" s="2">
-        <v>0.03129890561103821</v>
+        <v>0.1084285080432892</v>
       </c>
       <c r="C38" s="1">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="D38" s="1">
         <v>0</v>
       </c>
       <c r="E38" s="1">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F38" s="1">
         <v>0</v>
@@ -2402,56 +2420,108 @@
         <v>37</v>
       </c>
       <c r="B39" s="2">
-        <v>0.0156494528055191</v>
+        <v>0.02891426905989647</v>
       </c>
       <c r="C39" s="1">
+        <v>8</v>
+      </c>
+      <c r="D39" s="1">
+        <v>0</v>
+      </c>
+      <c r="E39" s="1">
+        <v>8</v>
+      </c>
+      <c r="F39" s="1">
+        <v>0</v>
+      </c>
+      <c r="G39" s="1">
+        <v>0</v>
+      </c>
+      <c r="H39" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="2">
+        <v>0.02891426905989647</v>
+      </c>
+      <c r="C40" s="1">
+        <v>8</v>
+      </c>
+      <c r="D40" s="1">
+        <v>0</v>
+      </c>
+      <c r="E40" s="1">
+        <v>8</v>
+      </c>
+      <c r="F40" s="1">
+        <v>0</v>
+      </c>
+      <c r="G40" s="1">
+        <v>0</v>
+      </c>
+      <c r="H40" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" s="2">
+        <v>0.01445713452994824</v>
+      </c>
+      <c r="C41" s="1">
         <v>4</v>
       </c>
-      <c r="D39" s="1">
-        <v>0</v>
-      </c>
-      <c r="E39" s="1">
+      <c r="D41" s="1">
+        <v>0</v>
+      </c>
+      <c r="E41" s="1">
         <v>4</v>
       </c>
-      <c r="F39" s="1">
-        <v>0</v>
-      </c>
-      <c r="G39" s="1">
-        <v>0</v>
-      </c>
-      <c r="H39" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" t="s">
-        <v>39</v>
-      </c>
-      <c r="B40">
+      <c r="F41" s="1">
+        <v>0</v>
+      </c>
+      <c r="G41" s="1">
+        <v>0</v>
+      </c>
+      <c r="H41" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42">
         <f>SUBTOTAL(109,[flash_percent])</f>
         <v>0</v>
       </c>
-      <c r="C40">
+      <c r="C42">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="D40">
+      <c r="D42">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="E40">
+      <c r="E42">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F40">
+      <c r="F42">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G40">
+      <c r="G42">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H40">
+      <c r="H42">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>

--- a/MDK-ARM/panzer_analysis.xlsx
+++ b/MDK-ARM/panzer_analysis.xlsx
@@ -86,13 +86,13 @@
     <t>mc_w.l</t>
   </si>
   <si>
+    <t>dmul.o</t>
+  </si>
+  <si>
+    <t>dma.o</t>
+  </si>
+  <si>
     <t>bule_car_control.o</t>
-  </si>
-  <si>
-    <t>dmul.o</t>
-  </si>
-  <si>
-    <t>dma.o</t>
   </si>
   <si>
     <t>gpio.o</t>
@@ -303,37 +303,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="40"/>
                 <c:pt idx="0">
-                  <c:v>30.63533592224121</c:v>
+                  <c:v>30.59982681274414</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>29.70699119567871</c:v>
+                  <c:v>29.67255783081055</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>17.8706111907959</c:v>
+                  <c:v>17.84989929199219</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>10.44386386871338</c:v>
+                  <c:v>10.43175888061523</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.829416990280151</c:v>
+                  <c:v>3.940886735916138</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.36524510383606</c:v>
+                  <c:v>3.361344575881958</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.959094762802124</c:v>
+                  <c:v>2.955665111541748</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.5802146792411804</c:v>
+                  <c:v>0.5795421600341797</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.2610965967178345</c:v>
+                  <c:v>0.2607939839363098</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.2320858687162399</c:v>
+                  <c:v>0.2318168580532074</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.11604293435812</c:v>
+                  <c:v>0.1159084290266037</c:v>
                 </c:pt>
                 <c:pt idx="39">
                   <c:v>0</c:v>
@@ -467,13 +467,13 @@
                   <c:v>stm32f4xx_hal.o</c:v>
                 </c:pt>
                 <c:pt idx="20">
+                  <c:v>dmul.o</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>dma.o</c:v>
+                </c:pt>
+                <c:pt idx="22">
                   <c:v>bule_car_control.o</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>dmul.o</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>dma.o</c:v>
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>gpio.o</c:v>
@@ -536,121 +536,121 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="40"/>
                 <c:pt idx="0">
-                  <c:v>16.46667671203613</c:v>
+                  <c:v>16.27840423583984</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>13.82824897766113</c:v>
+                  <c:v>13.67014408111572</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9.563394546508789</c:v>
+                  <c:v>9.454051971435547</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7.597224235534668</c:v>
+                  <c:v>8.760897636413574</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7.503252983093262</c:v>
+                  <c:v>7.417464733123779</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.573225498199463</c:v>
+                  <c:v>5.509503841400147</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.843140125274658</c:v>
+                  <c:v>4.787765979766846</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.72271203994751</c:v>
+                  <c:v>3.680148601531982</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.599826574325562</c:v>
+                  <c:v>3.558667898178101</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.41188383102417</c:v>
+                  <c:v>3.372874021530151</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3.339598178863525</c:v>
+                  <c:v>3.301414966583252</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3.24924111366272</c:v>
+                  <c:v>3.212090969085693</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.814370393753052</c:v>
+                  <c:v>1.793625831604004</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.742084741592407</c:v>
+                  <c:v>1.722166657447815</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.590284824371338</c:v>
+                  <c:v>1.572102308273315</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.546913385391235</c:v>
+                  <c:v>1.529226779937744</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.178256511688232</c:v>
+                  <c:v>1.164784908294678</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.105970740318298</c:v>
+                  <c:v>1.093325734138489</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.062599420547485</c:v>
+                  <c:v>1.050450205802918</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.9939280152320862</c:v>
+                  <c:v>0.9825639724731445</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.874656617641449</c:v>
+                  <c:v>0.8146348595619202</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.8240566849708557</c:v>
+                  <c:v>0.7931970953941345</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.8023709654808044</c:v>
+                  <c:v>0.75746750831604</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.7156281471252441</c:v>
+                  <c:v>0.7074460387229919</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.6722567677497864</c:v>
+                  <c:v>0.6645705103874207</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.5638282299041748</c:v>
+                  <c:v>0.5573817491531372</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.3541997969150543</c:v>
+                  <c:v>0.35015007853508</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.267456978559494</c:v>
+                  <c:v>0.2643990218639374</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.1807141751050949</c:v>
+                  <c:v>0.1786479949951172</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.1734856218099594</c:v>
+                  <c:v>0.1715020686388016</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.1662570536136627</c:v>
+                  <c:v>0.1643561571836472</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.137342780828476</c:v>
+                  <c:v>0.1357724666595459</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.1301142126321793</c:v>
+                  <c:v>0.1286265552043915</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.1156570762395859</c:v>
+                  <c:v>0.1143347173929215</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.1084285080432892</c:v>
+                  <c:v>0.1071887984871864</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.1084285080432892</c:v>
+                  <c:v>0.1071887984871864</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.02891426905989647</c:v>
+                  <c:v>0.02858367934823036</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.02891426905989647</c:v>
+                  <c:v>0.02858367934823036</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.01445713452994824</c:v>
+                  <c:v>0.01429183967411518</c:v>
                 </c:pt>
                 <c:pt idx="39">
                   <c:v>0</c:v>
@@ -1117,7 +1117,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>30.63533592224121</v>
+        <v>30.59982681274414</v>
       </c>
       <c r="C3" s="1">
         <v>1056</v>
@@ -1143,7 +1143,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>29.70699119567871</v>
+        <v>29.67255783081055</v>
       </c>
       <c r="C4" s="1">
         <v>1024</v>
@@ -1169,7 +1169,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>17.8706111907959</v>
+        <v>17.84989929199219</v>
       </c>
       <c r="C5" s="1">
         <v>616</v>
@@ -1195,7 +1195,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>10.44386386871338</v>
+        <v>10.43175888061523</v>
       </c>
       <c r="C6" s="1">
         <v>360</v>
@@ -1221,25 +1221,25 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>3.829416990280151</v>
+        <v>3.940886735916138</v>
       </c>
       <c r="C7" s="1">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="D7" s="1">
-        <v>2102</v>
+        <v>2452</v>
       </c>
       <c r="E7" s="1">
-        <v>2102</v>
+        <v>2442</v>
       </c>
       <c r="F7" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
       </c>
       <c r="H7" s="1">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1247,7 +1247,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>3.36524510383606</v>
+        <v>3.361344575881958</v>
       </c>
       <c r="C8" s="1">
         <v>116</v>
@@ -1273,7 +1273,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>2.959094762802124</v>
+        <v>2.955665111541748</v>
       </c>
       <c r="C9" s="1">
         <v>102</v>
@@ -1299,7 +1299,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>0.5802146792411804</v>
+        <v>0.5795421600341797</v>
       </c>
       <c r="C10" s="1">
         <v>20</v>
@@ -1325,7 +1325,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>0.2610965967178345</v>
+        <v>0.2607939839363098</v>
       </c>
       <c r="C11" s="1">
         <v>9</v>
@@ -1351,7 +1351,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.2320858687162399</v>
+        <v>0.2318168580532074</v>
       </c>
       <c r="C12" s="1">
         <v>8</v>
@@ -1377,7 +1377,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.11604293435812</v>
+        <v>0.1159084290266037</v>
       </c>
       <c r="C13" s="1">
         <v>4</v>
@@ -1484,7 +1484,7 @@
         <v>12</v>
       </c>
       <c r="B3" s="2">
-        <v>16.46667671203613</v>
+        <v>16.27840423583984</v>
       </c>
       <c r="C3" s="1">
         <v>4556</v>
@@ -1510,7 +1510,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="2">
-        <v>13.82824897766113</v>
+        <v>13.67014408111572</v>
       </c>
       <c r="C4" s="1">
         <v>3826</v>
@@ -1536,7 +1536,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="2">
-        <v>9.563394546508789</v>
+        <v>9.454051971435547</v>
       </c>
       <c r="C5" s="1">
         <v>2646</v>
@@ -1562,25 +1562,25 @@
         <v>5</v>
       </c>
       <c r="B6" s="2">
-        <v>7.597224235534668</v>
+        <v>8.760897636413574</v>
       </c>
       <c r="C6" s="1">
-        <v>2102</v>
+        <v>2452</v>
       </c>
       <c r="D6" s="1">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E6" s="1">
-        <v>2102</v>
+        <v>2442</v>
       </c>
       <c r="F6" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
       </c>
       <c r="H6" s="1">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1588,7 +1588,7 @@
         <v>15</v>
       </c>
       <c r="B7" s="2">
-        <v>7.503252983093262</v>
+        <v>7.417464733123779</v>
       </c>
       <c r="C7" s="1">
         <v>2076</v>
@@ -1614,7 +1614,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="2">
-        <v>5.573225498199463</v>
+        <v>5.509503841400147</v>
       </c>
       <c r="C8" s="1">
         <v>1542</v>
@@ -1640,7 +1640,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="2">
-        <v>4.843140125274658</v>
+        <v>4.787765979766846</v>
       </c>
       <c r="C9" s="1">
         <v>1340</v>
@@ -1666,7 +1666,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="2">
-        <v>3.72271203994751</v>
+        <v>3.680148601531982</v>
       </c>
       <c r="C10" s="1">
         <v>1030</v>
@@ -1692,7 +1692,7 @@
         <v>16</v>
       </c>
       <c r="B11" s="2">
-        <v>3.599826574325562</v>
+        <v>3.558667898178101</v>
       </c>
       <c r="C11" s="1">
         <v>996</v>
@@ -1718,7 +1718,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>3.41188383102417</v>
+        <v>3.372874021530151</v>
       </c>
       <c r="C12" s="1">
         <v>944</v>
@@ -1744,7 +1744,7 @@
         <v>6</v>
       </c>
       <c r="B13" s="2">
-        <v>3.339598178863525</v>
+        <v>3.301414966583252</v>
       </c>
       <c r="C13" s="1">
         <v>924</v>
@@ -1770,7 +1770,7 @@
         <v>7</v>
       </c>
       <c r="B14" s="2">
-        <v>3.24924111366272</v>
+        <v>3.212090969085693</v>
       </c>
       <c r="C14" s="1">
         <v>899</v>
@@ -1796,7 +1796,7 @@
         <v>17</v>
       </c>
       <c r="B15" s="2">
-        <v>1.814370393753052</v>
+        <v>1.793625831604004</v>
       </c>
       <c r="C15" s="1">
         <v>502</v>
@@ -1822,7 +1822,7 @@
         <v>18</v>
       </c>
       <c r="B16" s="2">
-        <v>1.742084741592407</v>
+        <v>1.722166657447815</v>
       </c>
       <c r="C16" s="1">
         <v>482</v>
@@ -1848,7 +1848,7 @@
         <v>19</v>
       </c>
       <c r="B17" s="2">
-        <v>1.590284824371338</v>
+        <v>1.572102308273315</v>
       </c>
       <c r="C17" s="1">
         <v>440</v>
@@ -1874,7 +1874,7 @@
         <v>2</v>
       </c>
       <c r="B18" s="2">
-        <v>1.546913385391235</v>
+        <v>1.529226779937744</v>
       </c>
       <c r="C18" s="1">
         <v>428</v>
@@ -1900,7 +1900,7 @@
         <v>20</v>
       </c>
       <c r="B19" s="2">
-        <v>1.178256511688232</v>
+        <v>1.164784908294678</v>
       </c>
       <c r="C19" s="1">
         <v>326</v>
@@ -1926,7 +1926,7 @@
         <v>21</v>
       </c>
       <c r="B20" s="2">
-        <v>1.105970740318298</v>
+        <v>1.093325734138489</v>
       </c>
       <c r="C20" s="1">
         <v>306</v>
@@ -1952,7 +1952,7 @@
         <v>22</v>
       </c>
       <c r="B21" s="2">
-        <v>1.062599420547485</v>
+        <v>1.050450205802918</v>
       </c>
       <c r="C21" s="1">
         <v>294</v>
@@ -1978,7 +1978,7 @@
         <v>9</v>
       </c>
       <c r="B22" s="2">
-        <v>0.9939280152320862</v>
+        <v>0.9825639724731445</v>
       </c>
       <c r="C22" s="1">
         <v>275</v>
@@ -2004,16 +2004,16 @@
         <v>23</v>
       </c>
       <c r="B23" s="2">
-        <v>0.874656617641449</v>
+        <v>0.8146348595619202</v>
       </c>
       <c r="C23" s="1">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="D23" s="1">
         <v>0</v>
       </c>
       <c r="E23" s="1">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="F23" s="1">
         <v>0</v>
@@ -2030,16 +2030,16 @@
         <v>24</v>
       </c>
       <c r="B24" s="2">
-        <v>0.8240566849708557</v>
+        <v>0.7931970953941345</v>
       </c>
       <c r="C24" s="1">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="D24" s="1">
         <v>0</v>
       </c>
       <c r="E24" s="1">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="F24" s="1">
         <v>0</v>
@@ -2056,16 +2056,16 @@
         <v>25</v>
       </c>
       <c r="B25" s="2">
-        <v>0.8023709654808044</v>
+        <v>0.75746750831604</v>
       </c>
       <c r="C25" s="1">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="D25" s="1">
         <v>0</v>
       </c>
       <c r="E25" s="1">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
@@ -2082,7 +2082,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="2">
-        <v>0.7156281471252441</v>
+        <v>0.7074460387229919</v>
       </c>
       <c r="C26" s="1">
         <v>198</v>
@@ -2108,7 +2108,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="2">
-        <v>0.6722567677497864</v>
+        <v>0.6645705103874207</v>
       </c>
       <c r="C27" s="1">
         <v>186</v>
@@ -2134,7 +2134,7 @@
         <v>8</v>
       </c>
       <c r="B28" s="2">
-        <v>0.5638282299041748</v>
+        <v>0.5573817491531372</v>
       </c>
       <c r="C28" s="1">
         <v>156</v>
@@ -2160,7 +2160,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="2">
-        <v>0.3541997969150543</v>
+        <v>0.35015007853508</v>
       </c>
       <c r="C29" s="1">
         <v>98</v>
@@ -2186,7 +2186,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="2">
-        <v>0.267456978559494</v>
+        <v>0.2643990218639374</v>
       </c>
       <c r="C30" s="1">
         <v>74</v>
@@ -2212,7 +2212,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="2">
-        <v>0.1807141751050949</v>
+        <v>0.1786479949951172</v>
       </c>
       <c r="C31" s="1">
         <v>50</v>
@@ -2238,7 +2238,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="2">
-        <v>0.1734856218099594</v>
+        <v>0.1715020686388016</v>
       </c>
       <c r="C32" s="1">
         <v>48</v>
@@ -2264,7 +2264,7 @@
         <v>11</v>
       </c>
       <c r="B33" s="2">
-        <v>0.1662570536136627</v>
+        <v>0.1643561571836472</v>
       </c>
       <c r="C33" s="1">
         <v>46</v>
@@ -2290,7 +2290,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="2">
-        <v>0.137342780828476</v>
+        <v>0.1357724666595459</v>
       </c>
       <c r="C34" s="1">
         <v>38</v>
@@ -2316,7 +2316,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="2">
-        <v>0.1301142126321793</v>
+        <v>0.1286265552043915</v>
       </c>
       <c r="C35" s="1">
         <v>36</v>
@@ -2342,7 +2342,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="2">
-        <v>0.1156570762395859</v>
+        <v>0.1143347173929215</v>
       </c>
       <c r="C36" s="1">
         <v>32</v>
@@ -2368,7 +2368,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="2">
-        <v>0.1084285080432892</v>
+        <v>0.1071887984871864</v>
       </c>
       <c r="C37" s="1">
         <v>30</v>
@@ -2394,7 +2394,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="2">
-        <v>0.1084285080432892</v>
+        <v>0.1071887984871864</v>
       </c>
       <c r="C38" s="1">
         <v>30</v>
@@ -2420,7 +2420,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="2">
-        <v>0.02891426905989647</v>
+        <v>0.02858367934823036</v>
       </c>
       <c r="C39" s="1">
         <v>8</v>
@@ -2446,7 +2446,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="2">
-        <v>0.02891426905989647</v>
+        <v>0.02858367934823036</v>
       </c>
       <c r="C40" s="1">
         <v>8</v>
@@ -2472,7 +2472,7 @@
         <v>39</v>
       </c>
       <c r="B41" s="2">
-        <v>0.01445713452994824</v>
+        <v>0.01429183967411518</v>
       </c>
       <c r="C41" s="1">
         <v>4</v>

--- a/MDK-ARM/panzer_analysis.xlsx
+++ b/MDK-ARM/panzer_analysis.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="46">
   <si>
     <t>panzer</t>
   </si>
@@ -35,10 +35,13 @@
     <t>bule_tooch.o</t>
   </si>
   <si>
+    <t>control_car.o</t>
+  </si>
+  <si>
     <t>interurp.o</t>
   </si>
   <si>
-    <t>control_car.o</t>
+    <t>usart_send_cloud.o</t>
   </si>
   <si>
     <t>emm_v5.o</t>
@@ -53,6 +56,9 @@
     <t>system_stm32f4xx.o</t>
   </si>
   <si>
+    <t>bule_car_control.o</t>
+  </si>
+  <si>
     <t>stm32f4xx_hal_tim.o</t>
   </si>
   <si>
@@ -68,9 +74,6 @@
     <t>stm32f4xx_hal_gpio.o</t>
   </si>
   <si>
-    <t>mf_w.l</t>
-  </si>
-  <si>
     <t>stm32f4xx_hal_cortex.o</t>
   </si>
   <si>
@@ -86,34 +89,19 @@
     <t>mc_w.l</t>
   </si>
   <si>
-    <t>dmul.o</t>
-  </si>
-  <si>
     <t>dma.o</t>
   </si>
   <si>
-    <t>bule_car_control.o</t>
-  </si>
-  <si>
     <t>gpio.o</t>
   </si>
   <si>
-    <t>depilogue.o</t>
-  </si>
-  <si>
     <t>uldiv.o</t>
   </si>
   <si>
     <t>stm32f4xx_hal_msp.o</t>
   </si>
   <si>
-    <t>dfixui.o</t>
-  </si>
-  <si>
     <t>init.o</t>
-  </si>
-  <si>
-    <t>f2d.o</t>
   </si>
   <si>
     <t>memseta.o</t>
@@ -254,9 +242,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>ram_percent!$A$3:$A$42</c:f>
+              <c:f>ram_percent!$A$3:$A$38</c:f>
               <c:strCache>
-                <c:ptCount val="40"/>
+                <c:ptCount val="36"/>
                 <c:pt idx="0">
                   <c:v>usart.o</c:v>
                 </c:pt>
@@ -273,24 +261,30 @@
                   <c:v>bule_tooch.o</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>control_car.o</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>interurp.o</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>control_car.o</c:v>
-                </c:pt>
                 <c:pt idx="7">
+                  <c:v>usart_send_cloud.o</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>emm_v5.o</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>stm32f4xx_hal.o</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>stm32f4xx_it.o</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>system_stm32f4xx.o</c:v>
                 </c:pt>
-                <c:pt idx="39">
+                <c:pt idx="12">
+                  <c:v>bule_car_control.o</c:v>
+                </c:pt>
+                <c:pt idx="35">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -298,44 +292,50 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>ram_percent!$B$3:$B$42</c:f>
+              <c:f>ram_percent!$B$3:$B$38</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="40"/>
+                <c:ptCount val="36"/>
                 <c:pt idx="0">
-                  <c:v>30.59982681274414</c:v>
+                  <c:v>29.85581016540527</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>29.67255783081055</c:v>
+                  <c:v>28.95108795166016</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>17.84989929199219</c:v>
+                  <c:v>17.41588973999023</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>10.43175888061523</c:v>
+                  <c:v>10.17811679840088</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.940886735916138</c:v>
+                  <c:v>3.845066547393799</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.361344575881958</c:v>
+                  <c:v>3.336160659790039</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.955665111541748</c:v>
+                  <c:v>3.27961540222168</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.5795421600341797</c:v>
+                  <c:v>1.86598813533783</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.2607939839363098</c:v>
+                  <c:v>0.5654509663581848</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.2318168580532074</c:v>
+                  <c:v>0.2544529139995575</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.1159084290266037</c:v>
-                </c:pt>
-                <c:pt idx="39">
+                  <c:v>0.226180374622345</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.1130901873111725</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.1130901873111725</c:v>
+                </c:pt>
+                <c:pt idx="35">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -403,9 +403,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>flash_percent!$A$3:$A$42</c:f>
+              <c:f>flash_percent!$A$3:$A$38</c:f>
               <c:strCache>
-                <c:ptCount val="40"/>
+                <c:ptCount val="36"/>
                 <c:pt idx="0">
                   <c:v>stm32f4xx_hal_tim.o</c:v>
                 </c:pt>
@@ -425,105 +425,93 @@
                   <c:v>usart.o</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>usart_send_cloud.o</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>tim.o</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>encode.o</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>stm32f4xx_hal_gpio.o</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>stm32f4xx_it.o</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>interurp.o</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>control_car.o</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>mf_w.l</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>stm32f4xx_hal_cortex.o</c:v>
                 </c:pt>
                 <c:pt idx="14">
+                  <c:v>bule_car_control.o</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>pid.o</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>startup_stm32f405xx.o</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>main.o</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
                   <c:v>stm32f4xx_hal_tim_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="19">
                   <c:v>mc_w.l</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="20">
                   <c:v>stm32f4xx_hal.o</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>dmul.o</c:v>
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>dma.o</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>bule_car_control.o</c:v>
+                  <c:v>gpio.o</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>gpio.o</c:v>
+                  <c:v>emm_v5.o</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>depilogue.o</c:v>
+                  <c:v>uldiv.o</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>emm_v5.o</c:v>
+                  <c:v>stm32f4xx_hal_msp.o</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>uldiv.o</c:v>
+                  <c:v>init.o</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>stm32f4xx_hal_msp.o</c:v>
+                  <c:v>system_stm32f4xx.o</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>dfixui.o</c:v>
+                  <c:v>memseta.o</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>init.o</c:v>
+                  <c:v>llushr.o</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>system_stm32f4xx.o</c:v>
+                  <c:v>llshl.o</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>f2d.o</c:v>
+                  <c:v>handlers.o</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>memseta.o</c:v>
+                  <c:v>entry9a.o</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>llushr.o</c:v>
+                  <c:v>entry2.o</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>llshl.o</c:v>
+                  <c:v>entry5.o</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>handlers.o</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>entry9a.o</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>entry2.o</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>entry5.o</c:v>
-                </c:pt>
-                <c:pt idx="39">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -531,128 +519,116 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>flash_percent!$B$3:$B$42</c:f>
+              <c:f>flash_percent!$B$3:$B$38</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="40"/>
+                <c:ptCount val="36"/>
                 <c:pt idx="0">
-                  <c:v>16.27840423583984</c:v>
+                  <c:v>15.85136699676514</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>13.67014408111572</c:v>
+                  <c:v>13.31153011322022</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9.454051971435547</c:v>
+                  <c:v>9.206040382385254</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8.760897636413574</c:v>
+                  <c:v>8.531069755554199</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7.417464733123779</c:v>
+                  <c:v>7.222879409790039</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.509503841400147</c:v>
+                  <c:v>5.364971160888672</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.787765979766846</c:v>
+                  <c:v>5.232760429382324</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.680148601531982</c:v>
+                  <c:v>4.662167072296143</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.558667898178101</c:v>
+                  <c:v>3.583605766296387</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.372874021530151</c:v>
+                  <c:v>3.465312004089356</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3.301414966583252</c:v>
+                  <c:v>3.28439211845398</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3.212090969085693</c:v>
+                  <c:v>3.214807510375977</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.793625831604004</c:v>
+                  <c:v>3.211328268051148</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.722166657447815</c:v>
+                  <c:v>1.676988363265991</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.572102308273315</c:v>
+                  <c:v>1.537819266319275</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.529226779937744</c:v>
+                  <c:v>1.530860781669617</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.164784908294678</c:v>
+                  <c:v>1.489109992980957</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.093325734138489</c:v>
+                  <c:v>1.134228706359863</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.050450205802918</c:v>
+                  <c:v>1.06464409828186</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.9825639724731445</c:v>
+                  <c:v>1.022893309593201</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.8146348595619202</c:v>
+                  <c:v>0.9567880034446716</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.7931970953941345</c:v>
+                  <c:v>0.7723888158798218</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.75746750831604</c:v>
+                  <c:v>0.688887357711792</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.7074460387229919</c:v>
+                  <c:v>0.5427597165107727</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.6645705103874207</c:v>
+                  <c:v>0.3409644365310669</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.5573817491531372</c:v>
+                  <c:v>0.2574629485607147</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.35015007853508</c:v>
+                  <c:v>0.1670029908418655</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.2643990218639374</c:v>
+                  <c:v>0.1600445359945297</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.1786479949951172</c:v>
+                  <c:v>0.1252522468566895</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.1715020686388016</c:v>
+                  <c:v>0.1113353297114372</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.1643561571836472</c:v>
+                  <c:v>0.1043768674135208</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.1357724666595459</c:v>
+                  <c:v>0.1043768674135208</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.1286265552043915</c:v>
+                  <c:v>0.02783383242785931</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.1143347173929215</c:v>
+                  <c:v>0.02783383242785931</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.1071887984871864</c:v>
+                  <c:v>0.01391691621392965</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.1071887984871864</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>0.02858367934823036</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>0.02858367934823036</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>0.01429183967411518</c:v>
-                </c:pt>
-                <c:pt idx="39">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -757,8 +733,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H42" totalsRowCount="1">
-  <autoFilter ref="A2:H41"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H38" totalsRowCount="1">
+  <autoFilter ref="A2:H37"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="ram_percent" totalsRowFunction="sum"/>
@@ -774,8 +750,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H42" totalsRowCount="1">
-  <autoFilter ref="A2:H41"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H38" totalsRowCount="1">
+  <autoFilter ref="A2:H37"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="flash_percent" totalsRowFunction="sum"/>
@@ -1075,7 +1051,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -1088,28 +1064,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" t="s">
         <v>40</v>
       </c>
-      <c r="B2" t="s">
+      <c r="E2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F2" t="s">
         <v>42</v>
       </c>
-      <c r="C2" t="s">
+      <c r="G2" t="s">
         <v>43</v>
       </c>
-      <c r="D2" t="s">
+      <c r="H2" t="s">
         <v>44</v>
-      </c>
-      <c r="E2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H2" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1117,7 +1093,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>30.59982681274414</v>
+        <v>29.85581016540527</v>
       </c>
       <c r="C3" s="1">
         <v>1056</v>
@@ -1143,7 +1119,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>29.67255783081055</v>
+        <v>28.95108795166016</v>
       </c>
       <c r="C4" s="1">
         <v>1024</v>
@@ -1169,7 +1145,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>17.84989929199219</v>
+        <v>17.41588973999023</v>
       </c>
       <c r="C5" s="1">
         <v>616</v>
@@ -1195,7 +1171,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>10.43175888061523</v>
+        <v>10.17811679840088</v>
       </c>
       <c r="C6" s="1">
         <v>360</v>
@@ -1221,7 +1197,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>3.940886735916138</v>
+        <v>3.845066547393799</v>
       </c>
       <c r="C7" s="1">
         <v>136</v>
@@ -1247,25 +1223,25 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>3.361344575881958</v>
+        <v>3.336160659790039</v>
       </c>
       <c r="C8" s="1">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D8" s="1">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="E8" s="1">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="F8" s="1">
         <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="1">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1273,25 +1249,25 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>2.955665111541748</v>
+        <v>3.27961540222168</v>
       </c>
       <c r="C9" s="1">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="D9" s="1">
-        <v>899</v>
+        <v>924</v>
       </c>
       <c r="E9" s="1">
-        <v>898</v>
+        <v>924</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" s="1">
-        <v>101</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1299,16 +1275,16 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>0.5795421600341797</v>
+        <v>1.86598813533783</v>
       </c>
       <c r="C10" s="1">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="D10" s="1">
-        <v>156</v>
+        <v>1504</v>
       </c>
       <c r="E10" s="1">
-        <v>156</v>
+        <v>1504</v>
       </c>
       <c r="F10" s="1">
         <v>0</v>
@@ -1317,7 +1293,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="1">
-        <v>20</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1325,25 +1301,25 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>0.2607939839363098</v>
+        <v>0.5654509663581848</v>
       </c>
       <c r="C11" s="1">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D11" s="1">
-        <v>275</v>
+        <v>156</v>
       </c>
       <c r="E11" s="1">
-        <v>270</v>
+        <v>156</v>
       </c>
       <c r="F11" s="1">
         <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H11" s="1">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1351,25 +1327,25 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.2318168580532074</v>
+        <v>0.2544529139995575</v>
       </c>
       <c r="C12" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" s="1">
-        <v>944</v>
+        <v>275</v>
       </c>
       <c r="E12" s="1">
-        <v>944</v>
+        <v>270</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H12" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1377,56 +1353,108 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.1159084290266037</v>
+        <v>0.226180374622345</v>
       </c>
       <c r="C13" s="1">
+        <v>8</v>
+      </c>
+      <c r="D13" s="1">
+        <v>944</v>
+      </c>
+      <c r="E13" s="1">
+        <v>944</v>
+      </c>
+      <c r="F13" s="1">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0.1130901873111725</v>
+      </c>
+      <c r="C14" s="1">
         <v>4</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D14" s="1">
         <v>46</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E14" s="1">
         <v>18</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F14" s="1">
         <v>24</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G14" s="1">
         <v>4</v>
       </c>
-      <c r="H13" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8">
-      <c r="A42" t="s">
-        <v>41</v>
-      </c>
-      <c r="B42">
+      <c r="H14" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0.1130901873111725</v>
+      </c>
+      <c r="C15" s="1">
+        <v>4</v>
+      </c>
+      <c r="D15" s="1">
+        <v>442</v>
+      </c>
+      <c r="E15" s="1">
+        <v>442</v>
+      </c>
+      <c r="F15" s="1">
+        <v>0</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38">
         <f>SUBTOTAL(109,[ram_percent])</f>
         <v>0</v>
       </c>
-      <c r="C42">
+      <c r="C38">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="D42">
+      <c r="D38">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="E42">
+      <c r="E38">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F42">
+      <c r="F38">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G42">
+      <c r="G38">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H42">
+      <c r="H38">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>
@@ -1442,7 +1470,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -1455,36 +1483,36 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" t="s">
         <v>40</v>
       </c>
-      <c r="B2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H2" t="s">
         <v>44</v>
-      </c>
-      <c r="D2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H2" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B3" s="2">
-        <v>16.27840423583984</v>
+        <v>15.85136699676514</v>
       </c>
       <c r="C3" s="1">
         <v>4556</v>
@@ -1507,10 +1535,10 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B4" s="2">
-        <v>13.67014408111572</v>
+        <v>13.31153011322022</v>
       </c>
       <c r="C4" s="1">
         <v>3826</v>
@@ -1533,10 +1561,10 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B5" s="2">
-        <v>9.454051971435547</v>
+        <v>9.206040382385254</v>
       </c>
       <c r="C5" s="1">
         <v>2646</v>
@@ -1562,7 +1590,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2">
-        <v>8.760897636413574</v>
+        <v>8.531069755554199</v>
       </c>
       <c r="C6" s="1">
         <v>2452</v>
@@ -1585,10 +1613,10 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B7" s="2">
-        <v>7.417464733123779</v>
+        <v>7.222879409790039</v>
       </c>
       <c r="C7" s="1">
         <v>2076</v>
@@ -1614,7 +1642,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="2">
-        <v>5.509503841400147</v>
+        <v>5.364971160888672</v>
       </c>
       <c r="C8" s="1">
         <v>1542</v>
@@ -1637,19 +1665,19 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>4.787765979766846</v>
+        <v>5.232760429382324</v>
       </c>
       <c r="C9" s="1">
-        <v>1340</v>
+        <v>1504</v>
       </c>
       <c r="D9" s="1">
-        <v>360</v>
+        <v>66</v>
       </c>
       <c r="E9" s="1">
-        <v>1340</v>
+        <v>1504</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
@@ -1658,76 +1686,76 @@
         <v>0</v>
       </c>
       <c r="H9" s="1">
-        <v>360</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B10" s="2">
-        <v>3.680148601531982</v>
+        <v>4.662167072296143</v>
       </c>
       <c r="C10" s="1">
-        <v>1030</v>
+        <v>1340</v>
       </c>
       <c r="D10" s="1">
-        <v>616</v>
+        <v>360</v>
       </c>
       <c r="E10" s="1">
-        <v>814</v>
+        <v>1340</v>
       </c>
       <c r="F10" s="1">
         <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>216</v>
+        <v>0</v>
       </c>
       <c r="H10" s="1">
-        <v>400</v>
+        <v>360</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B11" s="2">
-        <v>3.558667898178101</v>
+        <v>3.583605766296387</v>
       </c>
       <c r="C11" s="1">
-        <v>996</v>
+        <v>1030</v>
       </c>
       <c r="D11" s="1">
-        <v>0</v>
+        <v>616</v>
       </c>
       <c r="E11" s="1">
-        <v>996</v>
+        <v>814</v>
       </c>
       <c r="F11" s="1">
         <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="H11" s="1">
-        <v>0</v>
+        <v>400</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B12" s="2">
-        <v>3.372874021530151</v>
+        <v>3.465312004089356</v>
       </c>
       <c r="C12" s="1">
-        <v>944</v>
+        <v>996</v>
       </c>
       <c r="D12" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E12" s="1">
-        <v>944</v>
+        <v>996</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
@@ -1736,24 +1764,24 @@
         <v>0</v>
       </c>
       <c r="H12" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>3.301414966583252</v>
+        <v>3.28439211845398</v>
       </c>
       <c r="C13" s="1">
-        <v>924</v>
+        <v>944</v>
       </c>
       <c r="D13" s="1">
-        <v>116</v>
+        <v>8</v>
       </c>
       <c r="E13" s="1">
-        <v>924</v>
+        <v>944</v>
       </c>
       <c r="F13" s="1">
         <v>0</v>
@@ -1762,7 +1790,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="1">
-        <v>116</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1770,59 +1798,59 @@
         <v>7</v>
       </c>
       <c r="B14" s="2">
-        <v>3.212090969085693</v>
+        <v>3.214807510375977</v>
       </c>
       <c r="C14" s="1">
-        <v>899</v>
+        <v>924</v>
       </c>
       <c r="D14" s="1">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="E14" s="1">
-        <v>898</v>
+        <v>924</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" s="1">
-        <v>101</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="B15" s="2">
-        <v>1.793625831604004</v>
+        <v>3.211328268051148</v>
       </c>
       <c r="C15" s="1">
-        <v>502</v>
+        <v>923</v>
       </c>
       <c r="D15" s="1">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="E15" s="1">
-        <v>502</v>
+        <v>922</v>
       </c>
       <c r="F15" s="1">
         <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" s="1">
-        <v>0</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16" s="2">
-        <v>1.722166657447815</v>
+        <v>1.676988363265991</v>
       </c>
       <c r="C16" s="1">
         <v>482</v>
@@ -1845,19 +1873,19 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B17" s="2">
-        <v>1.572102308273315</v>
+        <v>1.537819266319275</v>
       </c>
       <c r="C17" s="1">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D17" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E17" s="1">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
@@ -1866,59 +1894,59 @@
         <v>0</v>
       </c>
       <c r="H17" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="B18" s="2">
-        <v>1.529226779937744</v>
+        <v>1.530860781669617</v>
       </c>
       <c r="C18" s="1">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="D18" s="1">
-        <v>1024</v>
+        <v>0</v>
       </c>
       <c r="E18" s="1">
-        <v>36</v>
+        <v>440</v>
       </c>
       <c r="F18" s="1">
-        <v>392</v>
+        <v>0</v>
       </c>
       <c r="G18" s="1">
         <v>0</v>
       </c>
       <c r="H18" s="1">
-        <v>1024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="B19" s="2">
-        <v>1.164784908294678</v>
+        <v>1.489109992980957</v>
       </c>
       <c r="C19" s="1">
-        <v>326</v>
+        <v>428</v>
       </c>
       <c r="D19" s="1">
-        <v>0</v>
+        <v>1024</v>
       </c>
       <c r="E19" s="1">
-        <v>326</v>
+        <v>36</v>
       </c>
       <c r="F19" s="1">
-        <v>0</v>
+        <v>392</v>
       </c>
       <c r="G19" s="1">
         <v>0</v>
       </c>
       <c r="H19" s="1">
-        <v>0</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1926,16 +1954,16 @@
         <v>21</v>
       </c>
       <c r="B20" s="2">
-        <v>1.093325734138489</v>
+        <v>1.134228706359863</v>
       </c>
       <c r="C20" s="1">
-        <v>306</v>
+        <v>326</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
       </c>
       <c r="E20" s="1">
-        <v>306</v>
+        <v>326</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
@@ -1952,16 +1980,16 @@
         <v>22</v>
       </c>
       <c r="B21" s="2">
-        <v>1.050450205802918</v>
+        <v>1.06464409828186</v>
       </c>
       <c r="C21" s="1">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="D21" s="1">
         <v>0</v>
       </c>
       <c r="E21" s="1">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
@@ -1975,54 +2003,54 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="B22" s="2">
-        <v>0.9825639724731445</v>
+        <v>1.022893309593201</v>
       </c>
       <c r="C22" s="1">
-        <v>275</v>
+        <v>294</v>
       </c>
       <c r="D22" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E22" s="1">
-        <v>270</v>
+        <v>294</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
       </c>
       <c r="G22" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H22" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B23" s="2">
-        <v>0.8146348595619202</v>
+        <v>0.9567880034446716</v>
       </c>
       <c r="C23" s="1">
-        <v>228</v>
+        <v>275</v>
       </c>
       <c r="D23" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E23" s="1">
-        <v>228</v>
+        <v>270</v>
       </c>
       <c r="F23" s="1">
         <v>0</v>
       </c>
       <c r="G23" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H23" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -2030,7 +2058,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="2">
-        <v>0.7931970953941345</v>
+        <v>0.7723888158798218</v>
       </c>
       <c r="C24" s="1">
         <v>222</v>
@@ -2056,16 +2084,16 @@
         <v>25</v>
       </c>
       <c r="B25" s="2">
-        <v>0.75746750831604</v>
+        <v>0.688887357711792</v>
       </c>
       <c r="C25" s="1">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="D25" s="1">
         <v>0</v>
       </c>
       <c r="E25" s="1">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
@@ -2079,19 +2107,19 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="B26" s="2">
-        <v>0.7074460387229919</v>
+        <v>0.5427597165107727</v>
       </c>
       <c r="C26" s="1">
-        <v>198</v>
+        <v>156</v>
       </c>
       <c r="D26" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E26" s="1">
-        <v>198</v>
+        <v>156</v>
       </c>
       <c r="F26" s="1">
         <v>0</v>
@@ -2100,24 +2128,24 @@
         <v>0</v>
       </c>
       <c r="H26" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B27" s="2">
-        <v>0.6645705103874207</v>
+        <v>0.3409644365310669</v>
       </c>
       <c r="C27" s="1">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="D27" s="1">
         <v>0</v>
       </c>
       <c r="E27" s="1">
-        <v>186</v>
+        <v>98</v>
       </c>
       <c r="F27" s="1">
         <v>0</v>
@@ -2131,19 +2159,19 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="B28" s="2">
-        <v>0.5573817491531372</v>
+        <v>0.2574629485607147</v>
       </c>
       <c r="C28" s="1">
-        <v>156</v>
+        <v>74</v>
       </c>
       <c r="D28" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E28" s="1">
-        <v>156</v>
+        <v>74</v>
       </c>
       <c r="F28" s="1">
         <v>0</v>
@@ -2152,7 +2180,7 @@
         <v>0</v>
       </c>
       <c r="H28" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -2160,16 +2188,16 @@
         <v>28</v>
       </c>
       <c r="B29" s="2">
-        <v>0.35015007853508</v>
+        <v>0.1670029908418655</v>
       </c>
       <c r="C29" s="1">
-        <v>98</v>
+        <v>48</v>
       </c>
       <c r="D29" s="1">
         <v>0</v>
       </c>
       <c r="E29" s="1">
-        <v>98</v>
+        <v>48</v>
       </c>
       <c r="F29" s="1">
         <v>0</v>
@@ -2183,25 +2211,25 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B30" s="2">
-        <v>0.2643990218639374</v>
+        <v>0.1600445359945297</v>
       </c>
       <c r="C30" s="1">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="D30" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E30" s="1">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="F30" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G30" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H30" s="1">
         <v>0</v>
@@ -2209,19 +2237,19 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B31" s="2">
-        <v>0.1786479949951172</v>
+        <v>0.1252522468566895</v>
       </c>
       <c r="C31" s="1">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="D31" s="1">
         <v>0</v>
       </c>
       <c r="E31" s="1">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="F31" s="1">
         <v>0</v>
@@ -2235,19 +2263,19 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B32" s="2">
-        <v>0.1715020686388016</v>
+        <v>0.1113353297114372</v>
       </c>
       <c r="C32" s="1">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D32" s="1">
         <v>0</v>
       </c>
       <c r="E32" s="1">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="F32" s="1">
         <v>0</v>
@@ -2261,25 +2289,25 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="B33" s="2">
-        <v>0.1643561571836472</v>
+        <v>0.1043768674135208</v>
       </c>
       <c r="C33" s="1">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="D33" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E33" s="1">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F33" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G33" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H33" s="1">
         <v>0</v>
@@ -2290,16 +2318,16 @@
         <v>32</v>
       </c>
       <c r="B34" s="2">
-        <v>0.1357724666595459</v>
+        <v>0.1043768674135208</v>
       </c>
       <c r="C34" s="1">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D34" s="1">
         <v>0</v>
       </c>
       <c r="E34" s="1">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F34" s="1">
         <v>0</v>
@@ -2316,16 +2344,16 @@
         <v>33</v>
       </c>
       <c r="B35" s="2">
-        <v>0.1286265552043915</v>
+        <v>0.02783383242785931</v>
       </c>
       <c r="C35" s="1">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="D35" s="1">
         <v>0</v>
       </c>
       <c r="E35" s="1">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="F35" s="1">
         <v>0</v>
@@ -2342,16 +2370,16 @@
         <v>34</v>
       </c>
       <c r="B36" s="2">
-        <v>0.1143347173929215</v>
+        <v>0.02783383242785931</v>
       </c>
       <c r="C36" s="1">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="D36" s="1">
         <v>0</v>
       </c>
       <c r="E36" s="1">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F36" s="1">
         <v>0</v>
@@ -2368,16 +2396,16 @@
         <v>35</v>
       </c>
       <c r="B37" s="2">
-        <v>0.1071887984871864</v>
+        <v>0.01391691621392965</v>
       </c>
       <c r="C37" s="1">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="D37" s="1">
         <v>0</v>
       </c>
       <c r="E37" s="1">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F37" s="1">
         <v>0</v>
@@ -2390,138 +2418,34 @@
       </c>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B38" s="2">
-        <v>0.1071887984871864</v>
-      </c>
-      <c r="C38" s="1">
-        <v>30</v>
-      </c>
-      <c r="D38" s="1">
-        <v>0</v>
-      </c>
-      <c r="E38" s="1">
-        <v>30</v>
-      </c>
-      <c r="F38" s="1">
-        <v>0</v>
-      </c>
-      <c r="G38" s="1">
-        <v>0</v>
-      </c>
-      <c r="H38" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" s="1" t="s">
+      <c r="A38" t="s">
         <v>37</v>
       </c>
-      <c r="B39" s="2">
-        <v>0.02858367934823036</v>
-      </c>
-      <c r="C39" s="1">
-        <v>8</v>
-      </c>
-      <c r="D39" s="1">
-        <v>0</v>
-      </c>
-      <c r="E39" s="1">
-        <v>8</v>
-      </c>
-      <c r="F39" s="1">
-        <v>0</v>
-      </c>
-      <c r="G39" s="1">
-        <v>0</v>
-      </c>
-      <c r="H39" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="2">
-        <v>0.02858367934823036</v>
-      </c>
-      <c r="C40" s="1">
-        <v>8</v>
-      </c>
-      <c r="D40" s="1">
-        <v>0</v>
-      </c>
-      <c r="E40" s="1">
-        <v>8</v>
-      </c>
-      <c r="F40" s="1">
-        <v>0</v>
-      </c>
-      <c r="G40" s="1">
-        <v>0</v>
-      </c>
-      <c r="H40" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8">
-      <c r="A41" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B41" s="2">
-        <v>0.01429183967411518</v>
-      </c>
-      <c r="C41" s="1">
-        <v>4</v>
-      </c>
-      <c r="D41" s="1">
-        <v>0</v>
-      </c>
-      <c r="E41" s="1">
-        <v>4</v>
-      </c>
-      <c r="F41" s="1">
-        <v>0</v>
-      </c>
-      <c r="G41" s="1">
-        <v>0</v>
-      </c>
-      <c r="H41" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8">
-      <c r="A42" t="s">
-        <v>41</v>
-      </c>
-      <c r="B42">
+      <c r="B38">
         <f>SUBTOTAL(109,[flash_percent])</f>
         <v>0</v>
       </c>
-      <c r="C42">
+      <c r="C38">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="D42">
+      <c r="D38">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="E42">
+      <c r="E38">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F42">
+      <c r="F38">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G42">
+      <c r="G38">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H42">
+      <c r="H38">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>

--- a/MDK-ARM/panzer_analysis.xlsx
+++ b/MDK-ARM/panzer_analysis.xlsx
@@ -437,19 +437,19 @@
                   <c:v>stm32f4xx_hal_gpio.o</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>control_car.o</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>stm32f4xx_it.o</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>interurp.o</c:v>
                 </c:pt>
-                <c:pt idx="12">
-                  <c:v>control_car.o</c:v>
-                </c:pt>
                 <c:pt idx="13">
+                  <c:v>bule_car_control.o</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>stm32f4xx_hal_cortex.o</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>bule_car_control.o</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>pid.o</c:v>
@@ -524,109 +524,109 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="36"/>
                 <c:pt idx="0">
-                  <c:v>15.85136699676514</c:v>
+                  <c:v>15.85909175872803</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>13.31153011322022</c:v>
+                  <c:v>13.31801700592041</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9.206040382385254</c:v>
+                  <c:v>9.210526466369629</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8.531069755554199</c:v>
+                  <c:v>8.583959579467773</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7.222879409790039</c:v>
+                  <c:v>7.226399421691895</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.364971160888672</c:v>
+                  <c:v>5.3675856590271</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5.232760429382324</c:v>
+                  <c:v>5.235310554504395</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4.662167072296143</c:v>
+                  <c:v>4.664438724517822</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.583605766296387</c:v>
+                  <c:v>3.585352182388306</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.465312004089356</c:v>
+                  <c:v>3.467000722885132</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3.28439211845398</c:v>
+                  <c:v>3.296435594558716</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3.214807510375977</c:v>
+                  <c:v>3.285992860794067</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3.211328268051148</c:v>
+                  <c:v>2.812587022781372</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.676988363265991</c:v>
+                  <c:v>1.761347770690918</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.537819266319275</c:v>
+                  <c:v>1.677805662155151</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.530860781669617</c:v>
+                  <c:v>1.531606793403626</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.489109992980957</c:v>
+                  <c:v>1.489835739135742</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.134228706359863</c:v>
+                  <c:v>1.134781360626221</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.06464409828186</c:v>
+                  <c:v>1.065162897109985</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.022893309593201</c:v>
+                  <c:v>1.023391842842102</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.9567880034446716</c:v>
+                  <c:v>0.9572542309761047</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.7723888158798218</c:v>
+                  <c:v>0.7727652192115784</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.688887357711792</c:v>
+                  <c:v>0.689223051071167</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.5427597165107727</c:v>
+                  <c:v>0.5430242419242859</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.3409644365310669</c:v>
+                  <c:v>0.3411306142807007</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.2574629485607147</c:v>
+                  <c:v>0.2575884163379669</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.1670029908418655</c:v>
+                  <c:v>0.1670843809843063</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.1600445359945297</c:v>
+                  <c:v>0.1601225286722183</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.1252522468566895</c:v>
+                  <c:v>0.1253132820129395</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.1113353297114372</c:v>
+                  <c:v>0.111389584839344</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.1043768674135208</c:v>
+                  <c:v>0.104427732527256</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.1043768674135208</c:v>
+                  <c:v>0.104427732527256</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.02783383242785931</c:v>
+                  <c:v>0.02784739620983601</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.02783383242785931</c:v>
+                  <c:v>0.02784739620983601</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.01391691621392965</c:v>
+                  <c:v>0.013923698104918</c:v>
                 </c:pt>
                 <c:pt idx="35">
                   <c:v>0</c:v>
@@ -1203,10 +1203,10 @@
         <v>136</v>
       </c>
       <c r="D7" s="1">
-        <v>2452</v>
+        <v>2466</v>
       </c>
       <c r="E7" s="1">
-        <v>2442</v>
+        <v>2456</v>
       </c>
       <c r="F7" s="1">
         <v>10</v>
@@ -1229,10 +1229,10 @@
         <v>118</v>
       </c>
       <c r="D8" s="1">
-        <v>923</v>
+        <v>947</v>
       </c>
       <c r="E8" s="1">
-        <v>922</v>
+        <v>946</v>
       </c>
       <c r="F8" s="1">
         <v>0</v>
@@ -1255,10 +1255,10 @@
         <v>116</v>
       </c>
       <c r="D9" s="1">
-        <v>924</v>
+        <v>808</v>
       </c>
       <c r="E9" s="1">
-        <v>924</v>
+        <v>808</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
@@ -1411,10 +1411,10 @@
         <v>4</v>
       </c>
       <c r="D15" s="1">
-        <v>442</v>
+        <v>506</v>
       </c>
       <c r="E15" s="1">
-        <v>442</v>
+        <v>506</v>
       </c>
       <c r="F15" s="1">
         <v>0</v>
@@ -1512,7 +1512,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="2">
-        <v>15.85136699676514</v>
+        <v>15.85909175872803</v>
       </c>
       <c r="C3" s="1">
         <v>4556</v>
@@ -1538,7 +1538,7 @@
         <v>15</v>
       </c>
       <c r="B4" s="2">
-        <v>13.31153011322022</v>
+        <v>13.31801700592041</v>
       </c>
       <c r="C4" s="1">
         <v>3826</v>
@@ -1564,7 +1564,7 @@
         <v>16</v>
       </c>
       <c r="B5" s="2">
-        <v>9.206040382385254</v>
+        <v>9.210526466369629</v>
       </c>
       <c r="C5" s="1">
         <v>2646</v>
@@ -1590,16 +1590,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="2">
-        <v>8.531069755554199</v>
+        <v>8.583959579467773</v>
       </c>
       <c r="C6" s="1">
-        <v>2452</v>
+        <v>2466</v>
       </c>
       <c r="D6" s="1">
         <v>136</v>
       </c>
       <c r="E6" s="1">
-        <v>2442</v>
+        <v>2456</v>
       </c>
       <c r="F6" s="1">
         <v>10</v>
@@ -1616,7 +1616,7 @@
         <v>17</v>
       </c>
       <c r="B7" s="2">
-        <v>7.222879409790039</v>
+        <v>7.226399421691895</v>
       </c>
       <c r="C7" s="1">
         <v>2076</v>
@@ -1642,7 +1642,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="2">
-        <v>5.364971160888672</v>
+        <v>5.3675856590271</v>
       </c>
       <c r="C8" s="1">
         <v>1542</v>
@@ -1668,7 +1668,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>5.232760429382324</v>
+        <v>5.235310554504395</v>
       </c>
       <c r="C9" s="1">
         <v>1504</v>
@@ -1694,7 +1694,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="2">
-        <v>4.662167072296143</v>
+        <v>4.664438724517822</v>
       </c>
       <c r="C10" s="1">
         <v>1340</v>
@@ -1720,7 +1720,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="2">
-        <v>3.583605766296387</v>
+        <v>3.585352182388306</v>
       </c>
       <c r="C11" s="1">
         <v>1030</v>
@@ -1746,7 +1746,7 @@
         <v>18</v>
       </c>
       <c r="B12" s="2">
-        <v>3.465312004089356</v>
+        <v>3.467000722885132</v>
       </c>
       <c r="C12" s="1">
         <v>996</v>
@@ -1769,45 +1769,45 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B13" s="2">
-        <v>3.28439211845398</v>
+        <v>3.296435594558716</v>
       </c>
       <c r="C13" s="1">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="D13" s="1">
-        <v>8</v>
+        <v>118</v>
       </c>
       <c r="E13" s="1">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="F13" s="1">
         <v>0</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" s="1">
-        <v>8</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B14" s="2">
-        <v>3.214807510375977</v>
+        <v>3.285992860794067</v>
       </c>
       <c r="C14" s="1">
-        <v>924</v>
+        <v>944</v>
       </c>
       <c r="D14" s="1">
-        <v>116</v>
+        <v>8</v>
       </c>
       <c r="E14" s="1">
-        <v>924</v>
+        <v>944</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
@@ -1816,50 +1816,50 @@
         <v>0</v>
       </c>
       <c r="H14" s="1">
-        <v>116</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B15" s="2">
-        <v>3.211328268051148</v>
+        <v>2.812587022781372</v>
       </c>
       <c r="C15" s="1">
-        <v>923</v>
+        <v>808</v>
       </c>
       <c r="D15" s="1">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E15" s="1">
-        <v>922</v>
+        <v>808</v>
       </c>
       <c r="F15" s="1">
         <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" s="1">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B16" s="2">
-        <v>1.676988363265991</v>
+        <v>1.761347770690918</v>
       </c>
       <c r="C16" s="1">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="D16" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E16" s="1">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
@@ -1868,24 +1868,24 @@
         <v>0</v>
       </c>
       <c r="H16" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B17" s="2">
-        <v>1.537819266319275</v>
+        <v>1.677805662155151</v>
       </c>
       <c r="C17" s="1">
-        <v>442</v>
+        <v>482</v>
       </c>
       <c r="D17" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E17" s="1">
-        <v>442</v>
+        <v>482</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
@@ -1894,7 +1894,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1902,7 +1902,7 @@
         <v>20</v>
       </c>
       <c r="B18" s="2">
-        <v>1.530860781669617</v>
+        <v>1.531606793403626</v>
       </c>
       <c r="C18" s="1">
         <v>440</v>
@@ -1928,7 +1928,7 @@
         <v>2</v>
       </c>
       <c r="B19" s="2">
-        <v>1.489109992980957</v>
+        <v>1.489835739135742</v>
       </c>
       <c r="C19" s="1">
         <v>428</v>
@@ -1954,7 +1954,7 @@
         <v>21</v>
       </c>
       <c r="B20" s="2">
-        <v>1.134228706359863</v>
+        <v>1.134781360626221</v>
       </c>
       <c r="C20" s="1">
         <v>326</v>
@@ -1980,7 +1980,7 @@
         <v>22</v>
       </c>
       <c r="B21" s="2">
-        <v>1.06464409828186</v>
+        <v>1.065162897109985</v>
       </c>
       <c r="C21" s="1">
         <v>306</v>
@@ -2006,7 +2006,7 @@
         <v>23</v>
       </c>
       <c r="B22" s="2">
-        <v>1.022893309593201</v>
+        <v>1.023391842842102</v>
       </c>
       <c r="C22" s="1">
         <v>294</v>
@@ -2032,7 +2032,7 @@
         <v>10</v>
       </c>
       <c r="B23" s="2">
-        <v>0.9567880034446716</v>
+        <v>0.9572542309761047</v>
       </c>
       <c r="C23" s="1">
         <v>275</v>
@@ -2058,7 +2058,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="2">
-        <v>0.7723888158798218</v>
+        <v>0.7727652192115784</v>
       </c>
       <c r="C24" s="1">
         <v>222</v>
@@ -2084,7 +2084,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="2">
-        <v>0.688887357711792</v>
+        <v>0.689223051071167</v>
       </c>
       <c r="C25" s="1">
         <v>198</v>
@@ -2110,7 +2110,7 @@
         <v>9</v>
       </c>
       <c r="B26" s="2">
-        <v>0.5427597165107727</v>
+        <v>0.5430242419242859</v>
       </c>
       <c r="C26" s="1">
         <v>156</v>
@@ -2136,7 +2136,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="2">
-        <v>0.3409644365310669</v>
+        <v>0.3411306142807007</v>
       </c>
       <c r="C27" s="1">
         <v>98</v>
@@ -2162,7 +2162,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="2">
-        <v>0.2574629485607147</v>
+        <v>0.2575884163379669</v>
       </c>
       <c r="C28" s="1">
         <v>74</v>
@@ -2188,7 +2188,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="2">
-        <v>0.1670029908418655</v>
+        <v>0.1670843809843063</v>
       </c>
       <c r="C29" s="1">
         <v>48</v>
@@ -2214,7 +2214,7 @@
         <v>12</v>
       </c>
       <c r="B30" s="2">
-        <v>0.1600445359945297</v>
+        <v>0.1601225286722183</v>
       </c>
       <c r="C30" s="1">
         <v>46</v>
@@ -2240,7 +2240,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="2">
-        <v>0.1252522468566895</v>
+        <v>0.1253132820129395</v>
       </c>
       <c r="C31" s="1">
         <v>36</v>
@@ -2266,7 +2266,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="2">
-        <v>0.1113353297114372</v>
+        <v>0.111389584839344</v>
       </c>
       <c r="C32" s="1">
         <v>32</v>
@@ -2292,7 +2292,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="2">
-        <v>0.1043768674135208</v>
+        <v>0.104427732527256</v>
       </c>
       <c r="C33" s="1">
         <v>30</v>
@@ -2318,7 +2318,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="2">
-        <v>0.1043768674135208</v>
+        <v>0.104427732527256</v>
       </c>
       <c r="C34" s="1">
         <v>30</v>
@@ -2344,7 +2344,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="2">
-        <v>0.02783383242785931</v>
+        <v>0.02784739620983601</v>
       </c>
       <c r="C35" s="1">
         <v>8</v>
@@ -2370,7 +2370,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="2">
-        <v>0.02783383242785931</v>
+        <v>0.02784739620983601</v>
       </c>
       <c r="C36" s="1">
         <v>8</v>
@@ -2396,7 +2396,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="2">
-        <v>0.01391691621392965</v>
+        <v>0.013923698104918</v>
       </c>
       <c r="C37" s="1">
         <v>4</v>
